--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="48" activeTab="54"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="18" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -60,8 +60,9 @@
     <sheet name="get_servo_status" sheetId="51" r:id="rId51"/>
     <sheet name="set_base_io_output" sheetId="52" r:id="rId52"/>
     <sheet name="set_digital_output" sheetId="53" r:id="rId53"/>
-    <sheet name="set_tool_reference" sheetId="54" r:id="rId54"/>
-    <sheet name="get_base_io_input" sheetId="55" r:id="rId55"/>
+    <sheet name="get_digital_input" sheetId="56" r:id="rId54"/>
+    <sheet name="set_tool_reference" sheetId="54" r:id="rId55"/>
+    <sheet name="get_base_io_input" sheetId="55" r:id="rId56"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="477">
   <si>
     <t>ID</t>
   </si>
@@ -605,6 +606,15 @@
     <t>[150.9, -93.7, 350, 179.85, -0.03, -92.57]</t>
   </si>
   <si>
+    <t>计算运动学正解</t>
+  </si>
+  <si>
+    <t>[0,40,-90,-20,0,0]</t>
+  </si>
+  <si>
+    <t>[111.0, -86.8, 360.6, -160.0, 0.0, -90.0]</t>
+  </si>
+  <si>
     <t>coords</t>
   </si>
   <si>
@@ -788,15 +798,12 @@
     <t>未暂停状态查询</t>
   </si>
   <si>
-    <t>恢复运动</t>
+    <t>恢复运动（缓启动）</t>
   </si>
   <si>
     <t>resume</t>
   </si>
   <si>
-    <t>恢复运动（缓启动）</t>
-  </si>
-  <si>
     <t>停止运动</t>
   </si>
   <si>
@@ -1430,6 +1437,15 @@
     <t>set_digital_output</t>
   </si>
   <si>
+    <t>读取1号引脚</t>
+  </si>
+  <si>
+    <t>读取2号引脚</t>
+  </si>
+  <si>
+    <t>读取引脚超限</t>
+  </si>
+  <si>
     <t>设置x轴工具坐标系</t>
   </si>
   <si>
@@ -1469,12 +1485,6 @@
     <t>[0,0,0,0,0,50]</t>
   </si>
   <si>
-    <t>读取1号引脚</t>
-  </si>
-  <si>
-    <t>读取2号引脚</t>
-  </si>
-  <si>
     <t>读取3号引脚</t>
   </si>
   <si>
@@ -1503,9 +1513,6 @@
   </si>
   <si>
     <t>读取12号引脚</t>
-  </si>
-  <si>
-    <t>读取引脚超限</t>
   </si>
 </sst>
 </file>
@@ -2697,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G5" s="1">
         <v>36</v>
@@ -3506,7 +3513,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
@@ -3529,7 +3536,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
@@ -3552,7 +3559,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
@@ -3575,7 +3582,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
@@ -3598,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
@@ -3621,7 +3628,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>8</v>
@@ -3644,7 +3651,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>8</v>
@@ -3667,7 +3674,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>8</v>
@@ -3690,7 +3697,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
@@ -3713,7 +3720,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
@@ -3736,7 +3743,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>8</v>
@@ -3759,7 +3766,7 @@
         <v>60</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>8</v>
@@ -3782,7 +3789,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>53</v>
@@ -3805,7 +3812,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>53</v>
@@ -3828,7 +3835,7 @@
         <v>20</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>53</v>
@@ -3851,7 +3858,7 @@
         <v>20</v>
       </c>
       <c r="F17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>53</v>
@@ -3874,7 +3881,7 @@
         <v>30</v>
       </c>
       <c r="F18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>53</v>
@@ -3897,7 +3904,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>53</v>
@@ -3920,7 +3927,7 @@
         <v>40</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>53</v>
@@ -3943,7 +3950,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>53</v>
@@ -3966,7 +3973,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>53</v>
@@ -3989,7 +3996,7 @@
         <v>50</v>
       </c>
       <c r="F23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>53</v>
@@ -4012,7 +4019,7 @@
         <v>100</v>
       </c>
       <c r="F24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -4035,7 +4042,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>53</v>
@@ -4600,7 +4607,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
@@ -4626,7 +4633,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>8</v>
@@ -4652,7 +4659,7 @@
         <v>70</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>8</v>
@@ -4678,7 +4685,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
@@ -4704,7 +4711,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>8</v>
@@ -4730,7 +4737,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>8</v>
@@ -4756,7 +4763,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>8</v>
@@ -4782,7 +4789,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -4808,7 +4815,7 @@
         <v>50</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -4834,7 +4841,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>8</v>
@@ -4860,7 +4867,7 @@
         <v>60</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
@@ -4886,7 +4893,7 @@
         <v>60</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>8</v>
@@ -4912,7 +4919,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
@@ -4938,7 +4945,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
@@ -4964,7 +4971,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
@@ -4990,7 +4997,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
@@ -5016,7 +5023,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
@@ -5042,7 +5049,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
@@ -5068,7 +5075,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
@@ -5094,7 +5101,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
@@ -5120,7 +5127,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -5146,7 +5153,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
@@ -5172,7 +5179,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -5198,7 +5205,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -5535,13 +5542,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="20.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="50" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
@@ -5601,7 +5608,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:6">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -5618,7 +5625,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:6">
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5635,7 +5642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:6">
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5652,7 +5659,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:6">
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -5666,6 +5673,26 @@
         <v>173</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5700,7 +5727,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>87</v>
@@ -5717,19 +5744,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E2" s="1">
         <v>20</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
@@ -5740,19 +5767,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
@@ -5763,19 +5790,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E4" s="1">
         <v>20</v>
       </c>
       <c r="F4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
@@ -5786,19 +5813,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E5" s="1">
         <v>20</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
@@ -5809,19 +5836,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E6" s="1">
         <v>30</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
@@ -5832,19 +5859,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E7" s="1">
         <v>30</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>8</v>
@@ -5855,19 +5882,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E8" s="1">
         <v>40</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>8</v>
@@ -5878,19 +5905,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E9" s="1">
         <v>40</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>8</v>
@@ -5901,19 +5928,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
@@ -5924,19 +5951,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
@@ -5947,19 +5974,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E12" s="1">
         <v>60</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>8</v>
@@ -5970,19 +5997,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E13" s="1">
         <v>60</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>8</v>
@@ -5993,19 +6020,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E14" s="1">
         <v>20</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>53</v>
@@ -6016,19 +6043,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>53</v>
@@ -6039,19 +6066,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E16" s="1">
         <v>20</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>53</v>
@@ -6062,19 +6089,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E17" s="1">
         <v>20</v>
       </c>
       <c r="F17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>53</v>
@@ -6085,19 +6112,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E18" s="1">
         <v>30</v>
       </c>
       <c r="F18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>53</v>
@@ -6108,19 +6135,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E19" s="1">
         <v>30</v>
       </c>
       <c r="F19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>53</v>
@@ -6131,19 +6158,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E20" s="1">
         <v>40</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>53</v>
@@ -6154,19 +6181,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E21" s="1">
         <v>40</v>
       </c>
       <c r="F21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>53</v>
@@ -6177,19 +6204,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="F22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>53</v>
@@ -6200,19 +6227,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="F23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>53</v>
@@ -6223,19 +6250,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E24" s="1">
         <v>100</v>
       </c>
       <c r="F24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -6246,19 +6273,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E25" s="1">
         <v>100</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>53</v>
@@ -6269,13 +6296,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>22</v>
@@ -6286,13 +6313,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>22</v>
@@ -6303,13 +6330,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>22</v>
@@ -6320,13 +6347,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>22</v>
@@ -6337,13 +6364,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>22</v>
@@ -6354,13 +6381,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>22</v>
@@ -6374,10 +6401,10 @@
         <v>148</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
@@ -6394,10 +6421,10 @@
         <v>148</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E33" s="1">
         <v>101</v>
@@ -6441,7 +6468,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>87</v>
@@ -6458,10 +6485,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6473,7 +6500,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
@@ -6484,10 +6511,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -6499,7 +6526,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>8</v>
@@ -6510,10 +6537,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -6525,7 +6552,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>8</v>
@@ -6536,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -6551,7 +6578,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
@@ -6562,10 +6589,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -6577,7 +6604,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>8</v>
@@ -6588,10 +6615,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6603,7 +6630,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>8</v>
@@ -6614,10 +6641,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -6629,7 +6656,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>8</v>
@@ -6640,10 +6667,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -6655,7 +6682,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -6666,10 +6693,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -6681,7 +6708,7 @@
         <v>50</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -6692,10 +6719,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -6707,7 +6734,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>8</v>
@@ -6718,10 +6745,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -6733,7 +6760,7 @@
         <v>60</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
@@ -6744,10 +6771,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -6759,7 +6786,7 @@
         <v>60</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>8</v>
@@ -6770,10 +6797,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -6785,7 +6812,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
@@ -6796,10 +6823,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -6811,7 +6838,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
@@ -6822,10 +6849,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -6837,7 +6864,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
@@ -6848,10 +6875,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -6863,7 +6890,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
@@ -6874,10 +6901,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -6889,7 +6916,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
@@ -6900,10 +6927,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -6915,7 +6942,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
@@ -6926,10 +6953,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
@@ -6941,7 +6968,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
@@ -6952,10 +6979,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D21" s="1">
         <v>4</v>
@@ -6967,7 +6994,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
@@ -6978,10 +7005,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D22" s="1">
         <v>5</v>
@@ -6993,7 +7020,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -7004,10 +7031,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
@@ -7019,7 +7046,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
@@ -7030,10 +7057,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D24" s="1">
         <v>6</v>
@@ -7045,7 +7072,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -7056,10 +7083,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
@@ -7071,7 +7098,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -7082,10 +7109,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -7102,10 +7129,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -7122,10 +7149,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -7142,10 +7169,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -7162,10 +7189,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -7182,10 +7209,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -7202,10 +7229,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -7225,10 +7252,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -7289,10 +7316,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -7309,10 +7336,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -7329,10 +7356,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -7346,10 +7373,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -7404,10 +7431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -7424,10 +7451,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -7448,8 +7475,8 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
@@ -7480,78 +7507,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="D2" s="1"/>
       <c r="E2" s="1">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -7600,10 +7571,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -7620,10 +7591,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -7640,10 +7611,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -7657,10 +7628,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -7719,13 +7690,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -7742,13 +7713,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -7765,13 +7736,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -7780,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
@@ -7788,13 +7759,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -7803,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
@@ -7811,13 +7782,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -7831,13 +7802,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E7" s="1">
         <v>-1</v>
@@ -7893,7 +7864,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -7946,10 +7917,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -7964,10 +7935,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -8014,10 +7985,10 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>87</v>
@@ -8037,7 +8008,7 @@
         <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -8066,7 +8037,7 @@
         <v>91</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -8095,7 +8066,7 @@
         <v>93</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -8124,7 +8095,7 @@
         <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -8153,7 +8124,7 @@
         <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -8182,7 +8153,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -8211,7 +8182,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -8240,7 +8211,7 @@
         <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -8269,7 +8240,7 @@
         <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -8298,7 +8269,7 @@
         <v>107</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -8327,7 +8298,7 @@
         <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -8356,7 +8327,7 @@
         <v>111</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -8385,7 +8356,7 @@
         <v>113</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -8414,7 +8385,7 @@
         <v>115</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -8443,7 +8414,7 @@
         <v>117</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -8472,7 +8443,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -8501,7 +8472,7 @@
         <v>121</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -8530,7 +8501,7 @@
         <v>122</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -8559,7 +8530,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -8588,7 +8559,7 @@
         <v>125</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -8617,7 +8588,7 @@
         <v>127</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -8646,7 +8617,7 @@
         <v>129</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -8675,7 +8646,7 @@
         <v>131</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -8704,7 +8675,7 @@
         <v>133</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -8733,7 +8704,7 @@
         <v>165</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -8760,7 +8731,7 @@
         <v>165</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -8784,10 +8755,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -8810,10 +8781,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -8836,10 +8807,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -8862,10 +8833,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
@@ -8919,7 +8890,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -8936,10 +8907,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -8962,10 +8933,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -8988,10 +8959,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -9014,10 +8985,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -9040,10 +9011,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -9066,10 +9037,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -9092,10 +9063,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -9118,10 +9089,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -9144,10 +9115,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -9170,10 +9141,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -9196,10 +9167,10 @@
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -9222,10 +9193,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -9251,7 +9222,7 @@
         <v>165</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -9275,7 +9246,7 @@
         <v>165</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -9296,10 +9267,10 @@
         <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -9320,10 +9291,10 @@
         <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -9344,10 +9315,10 @@
         <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -9368,10 +9339,10 @@
         <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D19" s="2">
         <v>4</v>
@@ -9423,7 +9394,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -9440,10 +9411,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -9466,10 +9437,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -9492,10 +9463,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -9518,10 +9489,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -9544,10 +9515,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -9562,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="27" spans="1:8">
@@ -9570,10 +9541,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -9596,10 +9567,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -9622,10 +9593,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -9648,10 +9619,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -9674,10 +9645,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -9700,10 +9671,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -9726,10 +9697,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -9752,10 +9723,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -9778,10 +9749,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -9804,10 +9775,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -9830,10 +9801,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -9856,10 +9827,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -9874,7 +9845,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="27" spans="1:8">
@@ -9882,10 +9853,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -9908,10 +9879,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -9934,10 +9905,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -9960,10 +9931,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -9986,10 +9957,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -10012,10 +9983,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -10038,10 +10009,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -10067,7 +10038,7 @@
         <v>165</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -10091,7 +10062,7 @@
         <v>165</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -10112,10 +10083,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -10136,10 +10107,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -10160,10 +10131,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -10184,10 +10155,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
@@ -10239,7 +10210,7 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -10256,10 +10227,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -10282,10 +10253,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -10308,10 +10279,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -10334,10 +10305,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -10360,10 +10331,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -10386,10 +10357,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -10412,10 +10383,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -10438,10 +10409,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -10464,10 +10435,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -10490,10 +10461,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -10516,10 +10487,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -10542,10 +10513,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -10568,10 +10539,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -10594,10 +10565,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -10620,10 +10591,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -10646,10 +10617,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -10672,10 +10643,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -10698,10 +10669,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -10724,10 +10695,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -10750,10 +10721,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -10776,10 +10747,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -10802,10 +10773,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -10828,10 +10799,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -10854,10 +10825,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -10883,7 +10854,7 @@
         <v>165</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -10907,7 +10878,7 @@
         <v>165</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -10928,10 +10899,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -10952,10 +10923,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -10976,10 +10947,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -11000,10 +10971,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -11055,7 +11026,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -11072,10 +11043,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -11098,10 +11069,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -11124,10 +11095,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -11150,10 +11121,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -11176,10 +11147,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -11202,10 +11173,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -11228,10 +11199,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -11254,10 +11225,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -11280,10 +11251,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -11306,10 +11277,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -11332,10 +11303,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -11358,10 +11329,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -11384,10 +11355,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -11410,10 +11381,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -11436,10 +11407,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -11462,10 +11433,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -11488,10 +11459,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -11514,10 +11485,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -11540,10 +11511,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -11566,10 +11537,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -11592,10 +11563,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -11618,10 +11589,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -11644,10 +11615,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -11670,10 +11641,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -11699,7 +11670,7 @@
         <v>165</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -11723,7 +11694,7 @@
         <v>165</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -11744,10 +11715,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -11768,10 +11739,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -11792,10 +11763,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -11816,10 +11787,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -11881,10 +11852,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11901,10 +11872,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -11921,10 +11892,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -11938,10 +11909,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -11999,10 +11970,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12022,10 +11993,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12045,10 +12016,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12065,10 +12036,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -12085,10 +12056,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -12105,10 +12076,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -12125,10 +12096,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -12145,10 +12116,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -12206,10 +12177,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12226,10 +12197,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12246,10 +12217,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12263,10 +12234,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -12324,10 +12295,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12347,10 +12318,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12370,10 +12341,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12390,10 +12361,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -12410,10 +12381,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -12430,10 +12401,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -12450,10 +12421,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -12470,10 +12441,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -12532,7 +12503,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -12584,10 +12555,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12604,10 +12575,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12624,10 +12595,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12644,10 +12615,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12664,10 +12635,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12684,10 +12655,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12704,10 +12675,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -12721,10 +12692,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -12782,10 +12753,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12805,10 +12776,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12828,10 +12799,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12851,10 +12822,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12874,10 +12845,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12897,10 +12868,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12920,10 +12891,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -12940,10 +12911,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -12963,7 +12934,7 @@
         <v>159</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -12983,7 +12954,7 @@
         <v>160</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -13003,7 +12974,7 @@
         <v>161</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -13023,7 +12994,7 @@
         <v>162</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D13" s="1">
         <v>4</v>
@@ -13043,7 +13014,7 @@
         <v>163</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
@@ -13063,7 +13034,7 @@
         <v>164</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -13121,10 +13092,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13141,10 +13112,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13161,10 +13132,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13181,10 +13152,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13201,10 +13172,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13221,10 +13192,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13241,10 +13212,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13258,10 +13229,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13319,10 +13290,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13342,10 +13313,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13365,10 +13336,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13388,10 +13359,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13411,10 +13382,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13434,10 +13405,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13457,10 +13428,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13477,10 +13448,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13500,7 +13471,7 @@
         <v>159</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -13520,7 +13491,7 @@
         <v>160</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -13540,7 +13511,7 @@
         <v>161</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -13560,7 +13531,7 @@
         <v>162</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D13" s="1">
         <v>4</v>
@@ -13580,7 +13551,7 @@
         <v>163</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
@@ -13600,7 +13571,7 @@
         <v>164</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -13657,10 +13628,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -13714,10 +13685,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13734,10 +13705,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13754,10 +13725,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13774,10 +13745,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13794,10 +13765,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13814,10 +13785,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13834,10 +13805,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13851,10 +13822,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13912,10 +13883,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13935,10 +13906,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -13958,10 +13929,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -13981,10 +13952,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14004,10 +13975,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14027,10 +13998,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14050,10 +14021,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14073,10 +14044,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14096,10 +14067,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14119,10 +14090,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14142,10 +14113,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14165,10 +14136,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14188,10 +14159,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -14208,10 +14179,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14228,10 +14199,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14248,10 +14219,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -14311,10 +14282,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14334,10 +14305,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14357,10 +14328,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14380,10 +14351,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14403,10 +14374,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14426,10 +14397,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14449,10 +14420,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14472,10 +14443,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14495,10 +14466,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14518,10 +14489,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14541,10 +14512,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14564,10 +14535,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14587,10 +14558,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D14" s="1">
         <v>254</v>
@@ -14610,10 +14581,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D15" s="1">
         <v>254</v>
@@ -14633,10 +14604,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -14653,10 +14624,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D17" s="1">
         <v>7</v>
@@ -14673,10 +14644,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -14693,10 +14664,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
@@ -14753,10 +14724,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -14808,14 +14779,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -14826,16 +14797,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="D3" s="2">
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -14940,14 +14911,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -14958,16 +14929,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D3" s="2">
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -15019,14 +14990,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15062,10 +15033,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -15079,16 +15050,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -15097,21 +15068,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -15120,21 +15091,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -15143,21 +15114,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -15166,21 +15137,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -15189,21 +15160,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="7" s="1" customFormat="1" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -15212,21 +15183,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="8" s="1" customFormat="1" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -15235,21 +15206,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="9" s="1" customFormat="1" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -15258,21 +15229,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="10" s="1" customFormat="1" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -15281,21 +15252,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="11" s="1" customFormat="1" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -15304,21 +15275,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="12" s="1" customFormat="1" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
@@ -15327,21 +15298,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="13" s="1" customFormat="1" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
@@ -15350,21 +15321,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="14" s="1" customFormat="1" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
       </c>
       <c r="E14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -15373,21 +15344,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="15" s="1" customFormat="1" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -15396,21 +15367,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="16" s="1" customFormat="1" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D16" s="1">
         <v>8</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
@@ -15419,21 +15390,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="17" s="1" customFormat="1" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D17" s="1">
         <v>8</v>
       </c>
       <c r="E17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
@@ -15442,21 +15413,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="18" s="1" customFormat="1" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D18" s="1">
         <v>9</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -15465,21 +15436,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="19" s="1" customFormat="1" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D19" s="1">
         <v>9</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
@@ -15488,21 +15459,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="27" spans="1:7">
+    <row r="20" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -15511,21 +15482,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" ht="27" spans="1:7">
+    <row r="21" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D21" s="1">
         <v>10</v>
       </c>
       <c r="E21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -15534,21 +15505,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" ht="27" spans="1:7">
+    <row r="22" spans="1:7">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D22" s="1">
         <v>11</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
@@ -15557,21 +15528,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" ht="27" spans="1:7">
+    <row r="23" spans="1:7">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D23" s="1">
         <v>11</v>
       </c>
       <c r="E23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1">
         <v>1</v>
@@ -15580,21 +15551,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" ht="27" spans="1:7">
+    <row r="24" spans="1:7">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D24" s="1">
         <v>12</v>
       </c>
       <c r="E24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
@@ -15603,21 +15574,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" ht="27" spans="1:7">
+    <row r="25" spans="1:7">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D25" s="1">
         <v>12</v>
       </c>
       <c r="E25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
@@ -15626,15 +15597,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" ht="27" spans="1:7">
+    <row r="26" spans="1:7">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
@@ -15646,15 +15617,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" ht="27" spans="1:7">
+    <row r="27" spans="1:7">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -15666,15 +15637,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" ht="27" spans="1:7">
+    <row r="28" spans="1:7">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -15686,15 +15657,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" ht="27" spans="1:7">
+    <row r="29" spans="1:7">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -15737,10 +15708,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -15754,16 +15725,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -15777,16 +15748,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -15800,16 +15771,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -15823,16 +15794,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -15846,10 +15817,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15866,10 +15837,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -15886,10 +15857,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -15906,10 +15877,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -15928,6 +15899,119 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G7"/>
@@ -15955,7 +16039,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -15969,16 +16053,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -15992,16 +16076,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -16015,16 +16099,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -16038,16 +16122,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -16061,16 +16145,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -16084,16 +16168,16 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -16108,7 +16192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F15"/>
@@ -16132,7 +16216,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -16146,10 +16230,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16166,10 +16250,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16186,10 +16270,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16206,10 +16290,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -16226,10 +16310,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -16246,10 +16330,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -16266,10 +16350,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -16286,10 +16370,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -16306,10 +16390,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
@@ -16326,10 +16410,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
@@ -16346,10 +16430,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D12" s="1">
         <v>11</v>
@@ -16366,10 +16450,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
@@ -16386,10 +16470,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
@@ -16403,10 +16487,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16582,7 +16666,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="18" activeTab="18"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="62" activeTab="69"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -63,6 +63,20 @@
     <sheet name="get_digital_input" sheetId="56" r:id="rId54"/>
     <sheet name="set_tool_reference" sheetId="54" r:id="rId55"/>
     <sheet name="get_base_io_input" sheetId="55" r:id="rId56"/>
+    <sheet name="get_tool_reference" sheetId="57" r:id="rId57"/>
+    <sheet name="set_world_reference" sheetId="58" r:id="rId58"/>
+    <sheet name="get_world_reference" sheetId="59" r:id="rId59"/>
+    <sheet name="set_reference_frame" sheetId="60" r:id="rId60"/>
+    <sheet name="get_reference_frame" sheetId="61" r:id="rId61"/>
+    <sheet name="set_movement_type" sheetId="62" r:id="rId62"/>
+    <sheet name="get_movement_type" sheetId="63" r:id="rId63"/>
+    <sheet name="set_end_type" sheetId="64" r:id="rId64"/>
+    <sheet name="get_end_type" sheetId="65" r:id="rId65"/>
+    <sheet name="get_vr_mode" sheetId="66" r:id="rId66"/>
+    <sheet name="set_vr_mode" sheetId="67" r:id="rId67"/>
+    <sheet name="get_filter_len" sheetId="68" r:id="rId68"/>
+    <sheet name="set_filter_len" sheetId="69" r:id="rId69"/>
+    <sheet name="get_fusion_parameters" sheetId="70" r:id="rId70"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="511">
   <si>
     <t>ID</t>
   </si>
@@ -1513,6 +1527,108 @@
   </si>
   <si>
     <t>读取12号引脚</t>
+  </si>
+  <si>
+    <t>获取工具坐标系</t>
+  </si>
+  <si>
+    <t>get_tool_reference</t>
+  </si>
+  <si>
+    <t>设置世界坐标系</t>
+  </si>
+  <si>
+    <t>set_world_reference</t>
+  </si>
+  <si>
+    <t>获取世界坐标系</t>
+  </si>
+  <si>
+    <t>get_world_reference</t>
+  </si>
+  <si>
+    <t>设置基坐标系</t>
+  </si>
+  <si>
+    <t>set_reference_frame</t>
+  </si>
+  <si>
+    <t>获取基坐标系</t>
+  </si>
+  <si>
+    <t>get_reference_frame</t>
+  </si>
+  <si>
+    <t>设置移动类型</t>
+  </si>
+  <si>
+    <t>set_movement_type</t>
+  </si>
+  <si>
+    <t>获取移动类型</t>
+  </si>
+  <si>
+    <t>get_movement_type</t>
+  </si>
+  <si>
+    <t>设置末端坐标系</t>
+  </si>
+  <si>
+    <t>set_end_type</t>
+  </si>
+  <si>
+    <t>获取末端坐标系</t>
+  </si>
+  <si>
+    <t>get_end_type</t>
+  </si>
+  <si>
+    <t>获取VR模式</t>
+  </si>
+  <si>
+    <t>get_vr_mode</t>
+  </si>
+  <si>
+    <t>设置VR模式</t>
+  </si>
+  <si>
+    <t>set_vr_mode</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>获取滤波器参数（拖动示教周期）</t>
+  </si>
+  <si>
+    <t>get_filter_len</t>
+  </si>
+  <si>
+    <t>获取滤波器参数超限</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>set_filter_len</t>
+  </si>
+  <si>
+    <t>获取速度融合规划参数（融合关节速度）</t>
+  </si>
+  <si>
+    <t>get_fusion_parameters</t>
+  </si>
+  <si>
+    <t>获取速度融合规划参数（融合关节加速度）</t>
+  </si>
+  <si>
+    <t>获取速度融合规划参数（融合坐标速度）</t>
+  </si>
+  <si>
+    <t>获取速度融合规划参数（融合坐标加速度）</t>
+  </si>
+  <si>
+    <t>获取速度融合规划参数超限</t>
   </si>
 </sst>
 </file>
@@ -5554,7 +5670,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15945,7 +16061,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15965,7 +16081,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -16505,6 +16621,184 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="42" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -16613,6 +16907,909 @@
       <c r="E5" s="4"/>
       <c r="F5" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="42" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="42" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="42" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
+    <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="42" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D4" s="2">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5">
+      <c r="E11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>120</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -16681,6 +17878,155 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:5">
+      <c r="A14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="62" activeTab="69"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="10" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -77,6 +77,8 @@
     <sheet name="get_filter_len" sheetId="68" r:id="rId68"/>
     <sheet name="set_filter_len" sheetId="69" r:id="rId69"/>
     <sheet name="get_fusion_parameters" sheetId="70" r:id="rId70"/>
+    <sheet name="set_fusion_parameters" sheetId="71" r:id="rId71"/>
+    <sheet name="solve_inv_kinematics" sheetId="72" r:id="rId72"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="501">
   <si>
     <t>ID</t>
   </si>
@@ -440,27 +442,15 @@
     <t>刷新模式下，使一关节运动到负限位</t>
   </si>
   <si>
-    <t>[-165,0,0,0,0,-50]</t>
-  </si>
-  <si>
     <t>刷新模式下，使一关节运动到正限位</t>
   </si>
   <si>
-    <t>[165,0,0,0,0,40]</t>
-  </si>
-  <si>
     <t>刷新模式下，使二关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,-120,90,0,0,20]</t>
-  </si>
-  <si>
     <t>刷新模式下，使二关节运动到正限位</t>
   </si>
   <si>
-    <t>[0,120,-90,0,0,-20]</t>
-  </si>
-  <si>
     <t>刷新模式下，使三关节运动到负限位</t>
   </si>
   <si>
@@ -470,37 +460,19 @@
     <t>刷新模式下，使四关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,10,0,-165,-90,0]</t>
-  </si>
-  <si>
     <t>刷新模式下，使四关节运动到正限位</t>
   </si>
   <si>
-    <t>[0,-10,0,165,0,0]</t>
-  </si>
-  <si>
     <t>刷新模式下，使五关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,20,0,0,-165,0]</t>
-  </si>
-  <si>
     <t>刷新模式下，使五关节运动到正限位</t>
   </si>
   <si>
-    <t>[0,-10,0,0,165,0]</t>
-  </si>
-  <si>
     <t>刷新模式下，使六关节运动到负限位</t>
   </si>
   <si>
-    <t>[10,0,0,30,0,-175]</t>
-  </si>
-  <si>
     <t>刷新模式下，使六关节运动到正限位</t>
-  </si>
-  <si>
-    <t>[-20,0,0,-30,0,175]</t>
   </si>
   <si>
     <t>全关节运动，角度超限</t>
@@ -2820,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G5" s="1">
         <v>36</v>
@@ -3899,13 +3871,13 @@
         <v>89</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="E14" s="1">
         <v>20</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>53</v>
@@ -3916,19 +3888,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>53</v>
@@ -3939,19 +3911,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="E16" s="1">
         <v>20</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>53</v>
@@ -3962,19 +3934,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="E17" s="1">
         <v>20</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>53</v>
@@ -3985,7 +3957,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>89</v>
@@ -3997,7 +3969,7 @@
         <v>30</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>53</v>
@@ -4008,7 +3980,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>89</v>
@@ -4020,7 +3992,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>53</v>
@@ -4031,19 +4003,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="E20" s="1">
         <v>40</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>53</v>
@@ -4054,19 +4026,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E21" s="1">
         <v>40</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>53</v>
@@ -4077,19 +4049,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>53</v>
@@ -4100,19 +4072,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>53</v>
@@ -4123,19 +4095,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="E24" s="1">
         <v>100</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -4146,19 +4118,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E25" s="1">
         <v>100</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>53</v>
@@ -4169,13 +4141,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>22</v>
@@ -4186,13 +4158,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>22</v>
@@ -4203,13 +4175,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>22</v>
@@ -4220,13 +4192,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>22</v>
@@ -4237,13 +4209,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>22</v>
@@ -4254,13 +4226,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>22</v>
@@ -4271,13 +4243,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>22</v>
@@ -4288,13 +4260,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>22</v>
@@ -4305,13 +4277,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>22</v>
@@ -4322,13 +4294,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>22</v>
@@ -4339,13 +4311,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>22</v>
@@ -4356,13 +4328,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>22</v>
@@ -4373,7 +4345,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>89</v>
@@ -4393,7 +4365,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>89</v>
@@ -4508,10 +4480,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -4528,10 +4500,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -4548,10 +4520,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -4568,10 +4540,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -4588,10 +4560,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -4608,10 +4580,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -4628,10 +4600,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -4645,10 +4617,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -4691,7 +4663,7 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>87</v>
@@ -4711,7 +4683,7 @@
         <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -4737,7 +4709,7 @@
         <v>91</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -4763,7 +4735,7 @@
         <v>93</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -4789,7 +4761,7 @@
         <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -4815,7 +4787,7 @@
         <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -4841,7 +4813,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -4867,7 +4839,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -4893,7 +4865,7 @@
         <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -4919,7 +4891,7 @@
         <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -4945,7 +4917,7 @@
         <v>107</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -4971,7 +4943,7 @@
         <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -4997,7 +4969,7 @@
         <v>111</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -5023,7 +4995,7 @@
         <v>113</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -5035,7 +5007,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
@@ -5046,10 +5018,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -5061,7 +5033,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
@@ -5072,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -5087,7 +5059,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
@@ -5098,10 +5070,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -5113,7 +5085,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
@@ -5124,10 +5096,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -5139,7 +5111,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
@@ -5150,10 +5122,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -5165,7 +5137,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
@@ -5176,10 +5148,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
@@ -5191,7 +5163,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
@@ -5202,10 +5174,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D21" s="1">
         <v>4</v>
@@ -5217,7 +5189,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
@@ -5228,10 +5200,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D22" s="1">
         <v>5</v>
@@ -5243,7 +5215,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -5254,10 +5226,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
@@ -5269,7 +5241,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
@@ -5280,10 +5252,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D24" s="1">
         <v>6</v>
@@ -5295,7 +5267,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -5306,10 +5278,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
@@ -5321,7 +5293,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -5332,10 +5304,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -5355,10 +5327,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -5378,10 +5350,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -5401,10 +5373,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -5424,10 +5396,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -5447,10 +5419,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -5470,10 +5442,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D32" s="1">
         <v>4</v>
@@ -5493,10 +5465,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D33" s="1">
         <v>4</v>
@@ -5516,10 +5488,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D34" s="1">
         <v>5</v>
@@ -5539,10 +5511,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D35" s="1">
         <v>5</v>
@@ -5562,10 +5534,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D36" s="1">
         <v>6</v>
@@ -5585,10 +5557,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D37" s="1">
         <v>6</v>
@@ -5608,10 +5580,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -5631,10 +5603,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D39" s="1">
         <v>4</v>
@@ -5695,13 +5667,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -5712,13 +5684,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -5729,13 +5701,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -5746,13 +5718,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -5763,13 +5735,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
@@ -5780,13 +5752,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -5797,16 +5769,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>8</v>
@@ -5843,7 +5815,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>87</v>
@@ -5860,13 +5832,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E2" s="1">
         <v>20</v>
@@ -5883,13 +5855,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E3" s="1">
         <v>50</v>
@@ -5906,13 +5878,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E4" s="1">
         <v>20</v>
@@ -5929,13 +5901,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E5" s="1">
         <v>20</v>
@@ -5952,13 +5924,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E6" s="1">
         <v>30</v>
@@ -5975,13 +5947,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E7" s="1">
         <v>30</v>
@@ -5998,13 +5970,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="E8" s="1">
         <v>40</v>
@@ -6021,13 +5993,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E9" s="1">
         <v>40</v>
@@ -6044,13 +6016,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
@@ -6067,13 +6039,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
@@ -6090,13 +6062,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E12" s="1">
         <v>60</v>
@@ -6113,13 +6085,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E13" s="1">
         <v>60</v>
@@ -6136,19 +6108,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E14" s="1">
         <v>20</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>53</v>
@@ -6159,19 +6131,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>53</v>
@@ -6182,19 +6154,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E16" s="1">
         <v>20</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>53</v>
@@ -6205,19 +6177,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E17" s="1">
         <v>20</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>53</v>
@@ -6228,19 +6200,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E18" s="1">
         <v>30</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>53</v>
@@ -6251,19 +6223,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E19" s="1">
         <v>30</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>53</v>
@@ -6274,19 +6246,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="E20" s="1">
         <v>40</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>53</v>
@@ -6297,19 +6269,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E21" s="1">
         <v>40</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>53</v>
@@ -6320,19 +6292,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>53</v>
@@ -6343,19 +6315,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E23" s="1">
         <v>50</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>53</v>
@@ -6366,19 +6338,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E24" s="1">
         <v>100</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -6389,19 +6361,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E25" s="1">
         <v>100</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>53</v>
@@ -6412,13 +6384,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>22</v>
@@ -6429,13 +6401,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>22</v>
@@ -6446,13 +6418,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>22</v>
@@ -6463,13 +6435,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>22</v>
@@ -6480,13 +6452,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>22</v>
@@ -6497,13 +6469,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>22</v>
@@ -6514,13 +6486,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
@@ -6534,13 +6506,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E33" s="1">
         <v>101</v>
@@ -6584,7 +6556,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>87</v>
@@ -6601,10 +6573,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6627,10 +6599,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -6653,10 +6625,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -6679,10 +6651,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -6705,10 +6677,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -6731,10 +6703,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6757,10 +6729,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -6783,10 +6755,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -6809,10 +6781,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -6835,10 +6807,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -6861,10 +6833,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -6887,10 +6859,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -6913,10 +6885,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -6928,7 +6900,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
@@ -6939,10 +6911,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -6954,7 +6926,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
@@ -6965,10 +6937,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -6980,7 +6952,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
@@ -6991,10 +6963,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -7006,7 +6978,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
@@ -7017,10 +6989,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -7032,7 +7004,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
@@ -7043,10 +7015,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -7058,7 +7030,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
@@ -7069,10 +7041,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
@@ -7084,7 +7056,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
@@ -7095,10 +7067,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D21" s="1">
         <v>4</v>
@@ -7110,7 +7082,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
@@ -7121,10 +7093,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D22" s="1">
         <v>5</v>
@@ -7136,7 +7108,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -7147,10 +7119,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
@@ -7162,7 +7134,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
@@ -7173,10 +7145,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D24" s="1">
         <v>6</v>
@@ -7188,7 +7160,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -7199,10 +7171,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
@@ -7214,7 +7186,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -7225,10 +7197,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -7245,10 +7217,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -7265,10 +7237,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -7285,10 +7257,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -7305,10 +7277,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -7325,10 +7297,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -7345,10 +7317,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -7368,10 +7340,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -7432,10 +7404,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -7452,10 +7424,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -7472,10 +7444,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -7489,10 +7461,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -7547,10 +7519,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -7567,10 +7539,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -7628,10 +7600,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -7687,10 +7659,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -7707,10 +7679,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -7727,10 +7699,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -7744,10 +7716,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -7806,13 +7778,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -7829,13 +7801,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -7852,13 +7824,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -7867,7 +7839,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
@@ -7875,13 +7847,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -7890,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
@@ -7898,13 +7870,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -7918,13 +7890,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E7" s="1">
         <v>-1</v>
@@ -8033,10 +8005,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -8051,10 +8023,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
@@ -8101,10 +8073,10 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>87</v>
@@ -8124,7 +8096,7 @@
         <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -8153,7 +8125,7 @@
         <v>91</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -8182,7 +8154,7 @@
         <v>93</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -8211,7 +8183,7 @@
         <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -8240,7 +8212,7 @@
         <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -8269,7 +8241,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -8298,7 +8270,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -8327,7 +8299,7 @@
         <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -8356,7 +8328,7 @@
         <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -8385,7 +8357,7 @@
         <v>107</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -8414,7 +8386,7 @@
         <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -8443,7 +8415,7 @@
         <v>111</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -8472,7 +8444,7 @@
         <v>113</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -8498,10 +8470,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -8527,10 +8499,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -8556,10 +8528,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -8585,10 +8557,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -8614,10 +8586,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -8643,10 +8615,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -8672,10 +8644,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -8701,10 +8673,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -8730,10 +8702,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -8759,10 +8731,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -8788,10 +8760,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -8817,10 +8789,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -8844,10 +8816,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -8871,10 +8843,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -8897,10 +8869,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -8923,10 +8895,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -8949,10 +8921,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
@@ -9006,7 +8978,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -9023,10 +8995,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -9049,10 +9021,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -9075,10 +9047,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -9101,10 +9073,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -9127,10 +9099,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -9153,10 +9125,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -9179,10 +9151,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -9205,10 +9177,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -9231,10 +9203,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -9257,10 +9229,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -9283,10 +9255,10 @@
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -9309,10 +9281,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -9335,10 +9307,10 @@
         <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -9359,10 +9331,10 @@
         <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -9383,10 +9355,10 @@
         <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -9407,10 +9379,10 @@
         <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -9431,10 +9403,10 @@
         <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -9455,10 +9427,10 @@
         <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D19" s="2">
         <v>4</v>
@@ -9510,7 +9482,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -9527,10 +9499,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -9553,10 +9525,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -9579,10 +9551,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -9605,10 +9577,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -9631,10 +9603,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -9649,7 +9621,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="27" spans="1:8">
@@ -9657,10 +9629,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -9683,10 +9655,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -9709,10 +9681,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -9735,10 +9707,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -9761,10 +9733,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -9787,10 +9759,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -9813,10 +9785,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -9839,10 +9811,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -9865,10 +9837,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -9891,10 +9863,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -9917,10 +9889,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -9943,10 +9915,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -9961,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="27" spans="1:8">
@@ -9969,10 +9941,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -9995,10 +9967,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -10021,10 +9993,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -10047,10 +10019,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -10073,10 +10045,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -10099,10 +10071,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -10125,10 +10097,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -10151,10 +10123,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -10175,10 +10147,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -10199,10 +10171,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -10223,10 +10195,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -10247,10 +10219,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -10271,10 +10243,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
@@ -10326,7 +10298,7 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -10343,10 +10315,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -10369,10 +10341,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -10395,10 +10367,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -10421,10 +10393,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -10447,10 +10419,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -10473,10 +10445,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -10499,10 +10471,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -10525,10 +10497,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -10551,10 +10523,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -10577,10 +10549,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -10603,10 +10575,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -10629,10 +10601,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -10655,10 +10627,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -10681,10 +10653,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -10707,10 +10679,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -10733,10 +10705,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -10759,10 +10731,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -10785,10 +10757,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -10811,10 +10783,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -10837,10 +10809,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -10863,10 +10835,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -10889,10 +10861,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -10915,10 +10887,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -10941,10 +10913,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -10967,10 +10939,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -10991,10 +10963,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -11015,10 +10987,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -11039,10 +11011,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -11063,10 +11035,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -11087,10 +11059,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -11142,7 +11114,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -11159,10 +11131,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -11185,10 +11157,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -11211,10 +11183,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -11237,10 +11209,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -11263,10 +11235,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -11289,10 +11261,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -11315,10 +11287,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -11341,10 +11313,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -11367,10 +11339,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -11393,10 +11365,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -11419,10 +11391,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -11445,10 +11417,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -11471,10 +11443,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -11497,10 +11469,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -11523,10 +11495,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -11549,10 +11521,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -11575,10 +11547,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -11601,10 +11573,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -11627,10 +11599,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -11653,10 +11625,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -11679,10 +11651,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -11705,10 +11677,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -11731,10 +11703,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -11757,10 +11729,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -11783,10 +11755,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -11807,10 +11779,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -11831,10 +11803,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -11855,10 +11827,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -11879,10 +11851,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -11903,10 +11875,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -11968,10 +11940,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11988,10 +11960,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12008,10 +11980,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12025,10 +11997,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -12086,10 +12058,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12109,10 +12081,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12132,10 +12104,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12152,10 +12124,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -12172,10 +12144,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -12192,10 +12164,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -12212,10 +12184,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -12232,10 +12204,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -12293,10 +12265,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12313,10 +12285,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12333,10 +12305,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12350,10 +12322,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -12411,10 +12383,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12434,10 +12406,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12457,10 +12429,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12477,10 +12449,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -12497,10 +12469,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -12517,10 +12489,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -12537,10 +12509,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -12557,10 +12529,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -12671,10 +12643,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12691,10 +12663,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12711,10 +12683,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12731,10 +12703,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12751,10 +12723,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12771,10 +12743,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12791,10 +12763,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -12808,10 +12780,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -12855,7 +12827,7 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -12869,10 +12841,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12892,10 +12864,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12915,10 +12887,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12938,10 +12910,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12961,10 +12933,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12984,10 +12956,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13007,10 +12979,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13027,10 +12999,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13047,10 +13019,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -13067,10 +13039,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -13087,10 +13059,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -13107,10 +13079,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D13" s="1">
         <v>4</v>
@@ -13127,10 +13099,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
@@ -13147,10 +13119,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -13208,10 +13180,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13228,10 +13200,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13248,10 +13220,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13268,10 +13240,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13288,10 +13260,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13308,10 +13280,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13328,10 +13300,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13345,10 +13317,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13392,7 +13364,7 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -13406,10 +13378,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13429,10 +13401,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13452,10 +13424,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13475,10 +13447,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13498,10 +13470,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13521,10 +13493,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13544,10 +13516,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13564,10 +13536,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13584,10 +13556,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -13604,10 +13576,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -13624,10 +13596,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -13644,10 +13616,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D13" s="1">
         <v>4</v>
@@ -13664,10 +13636,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
@@ -13684,10 +13656,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -13744,10 +13716,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -13801,10 +13773,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13821,10 +13793,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13841,10 +13813,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13861,10 +13833,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13881,10 +13853,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13901,10 +13873,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13921,10 +13893,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13938,10 +13910,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13999,10 +13971,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14022,10 +13994,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14045,10 +14017,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14068,10 +14040,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14091,10 +14063,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14114,10 +14086,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14137,10 +14109,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14160,10 +14132,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14183,10 +14155,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14206,10 +14178,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14229,10 +14201,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14252,10 +14224,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14275,10 +14247,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -14295,10 +14267,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14315,10 +14287,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14335,10 +14307,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -14398,10 +14370,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14421,10 +14393,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14444,10 +14416,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14467,10 +14439,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14490,10 +14462,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14513,10 +14485,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14536,10 +14508,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14559,10 +14531,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14582,10 +14554,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14605,10 +14577,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14628,10 +14600,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14651,10 +14623,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14674,10 +14646,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D14" s="1">
         <v>254</v>
@@ -14697,10 +14669,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D15" s="1">
         <v>254</v>
@@ -14720,10 +14692,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -14740,10 +14712,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D17" s="1">
         <v>7</v>
@@ -14760,10 +14732,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -14780,10 +14752,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
@@ -14840,10 +14812,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -14895,14 +14867,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -14913,16 +14885,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D3" s="2">
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -15027,14 +14999,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15045,16 +15017,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D3" s="2">
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -15106,14 +15078,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15149,10 +15121,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -15166,10 +15138,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15189,10 +15161,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15212,10 +15184,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15235,10 +15207,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15258,10 +15230,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15281,10 +15253,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15304,10 +15276,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15327,10 +15299,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15350,10 +15322,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15373,10 +15345,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15396,10 +15368,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15419,10 +15391,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15442,10 +15414,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15465,10 +15437,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15488,10 +15460,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D16" s="1">
         <v>8</v>
@@ -15511,10 +15483,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D17" s="1">
         <v>8</v>
@@ -15534,10 +15506,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D18" s="1">
         <v>9</v>
@@ -15557,10 +15529,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D19" s="1">
         <v>9</v>
@@ -15580,10 +15552,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
@@ -15603,10 +15575,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D21" s="1">
         <v>10</v>
@@ -15626,10 +15598,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D22" s="1">
         <v>11</v>
@@ -15649,10 +15621,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D23" s="1">
         <v>11</v>
@@ -15672,10 +15644,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D24" s="1">
         <v>12</v>
@@ -15695,10 +15667,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D25" s="1">
         <v>12</v>
@@ -15718,10 +15690,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
@@ -15738,10 +15710,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -15758,10 +15730,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -15778,10 +15750,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -15824,10 +15796,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -15841,10 +15813,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15864,10 +15836,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15887,10 +15859,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15910,10 +15882,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15933,10 +15905,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15953,10 +15925,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -15973,10 +15945,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -15993,10 +15965,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -16038,7 +16010,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -16052,10 +16024,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16072,10 +16044,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16092,10 +16064,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16109,10 +16081,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -16155,7 +16127,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -16169,16 +16141,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -16192,16 +16164,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -16215,16 +16187,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -16238,16 +16210,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -16261,16 +16233,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -16284,16 +16256,16 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -16332,7 +16304,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -16346,10 +16318,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16366,10 +16338,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16386,10 +16358,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16406,10 +16378,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -16426,10 +16398,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -16446,10 +16418,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -16466,10 +16438,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -16486,10 +16458,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -16506,10 +16478,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
@@ -16526,10 +16498,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
@@ -16546,10 +16518,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D12" s="1">
         <v>11</v>
@@ -16566,10 +16538,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
@@ -16586,10 +16558,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
@@ -16603,10 +16575,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16661,14 +16633,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -16705,7 +16677,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -16719,13 +16691,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -16780,14 +16752,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -16954,10 +16926,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -16974,10 +16946,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -16994,10 +16966,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -17011,10 +16983,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -17069,10 +17041,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1">
@@ -17091,8 +17063,8 @@
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
@@ -17122,18 +17094,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="42" customHeight="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -17142,18 +17114,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="27" customHeight="1" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -17167,13 +17139,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -17187,13 +17159,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -17207,17 +17179,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>234</v>
+        <v>477</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D6" s="2">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:6">
@@ -17225,16 +17199,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D7" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -17284,10 +17276,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1">
@@ -17342,10 +17334,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -17362,10 +17354,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -17382,10 +17374,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -17400,10 +17392,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -17459,10 +17451,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -17518,10 +17510,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -17576,10 +17568,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -17596,10 +17588,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -17616,10 +17608,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -17634,10 +17626,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -17679,7 +17671,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -17693,10 +17685,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="D2" s="2">
         <v>5</v>
@@ -17713,10 +17705,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -17730,10 +17722,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="D4" s="2">
         <v>6</v>
@@ -17777,10 +17769,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -17794,10 +17786,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="D2" s="2">
         <v>5</v>
@@ -17904,7 +17896,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -17918,15 +17910,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
+      <c r="E2" s="2">
+        <v>150</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
@@ -17936,13 +17930,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1000</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -17953,13 +17950,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -17970,13 +17970,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4000</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -17987,10 +17990,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -18004,10 +18007,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -18022,6 +18025,28 @@
       <c r="E14" s="2"/>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="10" activeTab="10"/>
+    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="36" activeTab="42"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="501">
   <si>
     <t>ID</t>
   </si>
@@ -12801,7 +12801,7 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
@@ -12850,7 +12850,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>-155</v>
+        <v>-100</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -12873,7 +12873,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>-110</v>
+        <v>-90</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -12896,7 +12896,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>-150</v>
+        <v>-120</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -12919,7 +12919,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>-155</v>
+        <v>-130</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -12942,7 +12942,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>-155</v>
+        <v>-130</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -12965,7 +12965,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>-160</v>
+        <v>-100</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -12979,19 +12979,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>245</v>
+        <v>358</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
         <v>-155</v>
       </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="27" spans="1:7">
@@ -12999,138 +13002,273 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>245</v>
+        <v>360</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D9" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E9" s="1">
         <v>-110</v>
       </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" ht="27" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="27" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>149</v>
+        <v>361</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1">
-        <v>-166</v>
+        <v>-150</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" ht="27" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="27" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>150</v>
+        <v>362</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1">
-        <v>-121</v>
+        <v>-155</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="27" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>151</v>
+        <v>363</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1">
-        <v>-159</v>
+        <v>-155</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" ht="27" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="27" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>364</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1">
-        <v>-166</v>
+        <v>-160</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" ht="27" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="27" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>-166</v>
+        <v>-155</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="27" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-110</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" ht="27" spans="1:7">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-166</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" ht="27" spans="1:7">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-121</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" ht="27" spans="1:7">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-159</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" ht="27" spans="1:7">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-166</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" ht="27" spans="1:7">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-166</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" ht="27" spans="1:7">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D21" s="1">
         <v>6</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E21" s="1">
         <v>-176</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -13338,7 +13476,7 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
@@ -13387,7 +13525,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -13410,7 +13548,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -13433,7 +13571,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -13456,7 +13594,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -13479,7 +13617,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -13502,7 +13640,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -13516,19 +13654,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
         <v>155</v>
       </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="27" spans="1:7">
@@ -13536,19 +13677,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>245</v>
+        <v>374</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D9" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E9" s="1">
         <v>110</v>
       </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="27" spans="1:7">
@@ -13556,19 +13700,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>149</v>
+        <v>375</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1">
-        <v>166</v>
+        <v>150</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="27" spans="1:7">
@@ -13576,19 +13723,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1">
-        <v>121</v>
+        <v>155</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="27" spans="1:7">
@@ -13596,19 +13746,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>151</v>
+        <v>377</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="27" spans="1:7">
@@ -13616,19 +13769,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>378</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1">
-        <v>166</v>
+        <v>160</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="27" spans="1:7">
@@ -13636,16 +13792,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>22</v>
@@ -13656,18 +13812,138 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>373</v>
       </c>
       <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>110</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="27" spans="1:7">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>166</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="27" spans="1:7">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>121</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="27" spans="1:7">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>159</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="27" spans="1:7">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>166</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="27" spans="1:7">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>166</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="27" spans="1:7">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D21" s="1">
         <v>6</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E21" s="1">
         <v>176</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="36" activeTab="42"/>
+    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="45" activeTab="51"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="45" activeTab="51"/>
+    <workbookView windowWidth="28155" windowHeight="13185" firstSheet="32" activeTab="34"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -253,7 +253,7 @@
     <t>[-8.75, -44.21, -7.2, 48.05, 8.98, 0.0]</t>
   </si>
   <si>
-    <t>奇异点报错清楚错误信息</t>
+    <t>奇异点报错清除错误信息</t>
   </si>
   <si>
     <t>clear_error_information</t>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="7">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -2656,7 +2656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:1">
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A3" s="2"/>
     </row>
   </sheetData>
@@ -2949,7 +2949,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:1">
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A3" s="2"/>
     </row>
   </sheetData>
@@ -3402,7 +3402,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:1">
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A3" s="2"/>
     </row>
   </sheetData>
@@ -3463,7 +3463,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:1">
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A3" s="2"/>
     </row>
   </sheetData>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="7">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -9826,7 +9826,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
@@ -9852,7 +9852,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
@@ -9878,7 +9878,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
@@ -9904,7 +9904,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
@@ -9930,7 +9930,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>267</v>
@@ -9956,7 +9956,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
@@ -9982,7 +9982,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
@@ -10008,7 +10008,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
@@ -10034,7 +10034,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -10060,7 +10060,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
@@ -10086,7 +10086,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -10112,7 +10112,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -10330,7 +10330,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
@@ -10356,7 +10356,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>8</v>
@@ -10382,7 +10382,7 @@
         <v>70</v>
       </c>
       <c r="G4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>8</v>
@@ -10408,7 +10408,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
@@ -10434,7 +10434,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>8</v>
@@ -10460,7 +10460,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>8</v>
@@ -10486,7 +10486,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>8</v>
@@ -10512,7 +10512,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -10538,7 +10538,7 @@
         <v>50</v>
       </c>
       <c r="G10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -10564,7 +10564,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>8</v>
@@ -10590,7 +10590,7 @@
         <v>60</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
@@ -10616,7 +10616,7 @@
         <v>60</v>
       </c>
       <c r="G13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>8</v>
@@ -10642,7 +10642,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
@@ -10668,7 +10668,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
@@ -10694,7 +10694,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
@@ -10720,7 +10720,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
@@ -10746,7 +10746,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
@@ -10772,7 +10772,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
@@ -10798,7 +10798,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
@@ -10824,7 +10824,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
@@ -10850,7 +10850,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -10876,7 +10876,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
@@ -10902,7 +10902,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -10928,7 +10928,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -11044,7 +11044,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="2">
-        <v>-166</v>
+        <v>-332</v>
       </c>
       <c r="F30" s="2">
         <v>50</v>
@@ -11068,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="2">
-        <v>166</v>
+        <v>332</v>
       </c>
       <c r="F31" s="2">
         <v>50</v>
@@ -11146,7 +11146,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
@@ -11172,7 +11172,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>8</v>
@@ -11198,7 +11198,7 @@
         <v>70</v>
       </c>
       <c r="G4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>8</v>
@@ -11224,7 +11224,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
@@ -11250,7 +11250,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>8</v>
@@ -11276,7 +11276,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>8</v>
@@ -11302,7 +11302,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>8</v>
@@ -11328,7 +11328,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -11354,7 +11354,7 @@
         <v>50</v>
       </c>
       <c r="G10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -11380,7 +11380,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>8</v>
@@ -11406,7 +11406,7 @@
         <v>60</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
@@ -11432,7 +11432,7 @@
         <v>60</v>
       </c>
       <c r="G13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>8</v>
@@ -11458,7 +11458,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
@@ -11484,7 +11484,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
@@ -11510,7 +11510,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
@@ -11536,7 +11536,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
@@ -11562,7 +11562,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
@@ -11588,7 +11588,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
@@ -11614,7 +11614,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
@@ -11640,7 +11640,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
@@ -11666,7 +11666,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
@@ -11692,7 +11692,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
@@ -11718,7 +11718,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
@@ -11744,7 +11744,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -11860,7 +11860,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="2">
-        <v>-467</v>
+        <v>-934</v>
       </c>
       <c r="F30" s="2">
         <v>50</v>
@@ -11884,7 +11884,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="2">
-        <v>467</v>
+        <v>934</v>
       </c>
       <c r="F31" s="2">
         <v>50</v>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -18010,7 +18010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="5:5">
+    <row r="11" spans="1:6">
       <c r="E11" s="2"/>
     </row>
   </sheetData>
@@ -18137,7 +18137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:1">
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A3" s="2"/>
     </row>
   </sheetData>
@@ -18295,7 +18295,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:5">
+    <row r="14" s="1" customFormat="1" spans="1:6">
       <c r="A14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -18613,7 +18613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:1">
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A3" s="2"/>
     </row>
   </sheetData>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28155" windowHeight="13185" firstSheet="32" activeTab="34"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="22" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -370,73 +370,73 @@
     <t>send_angles</t>
   </si>
   <si>
-    <t>[-165,0,0,0,0,10]</t>
+    <t>[-162,0,0,0,0,10]</t>
   </si>
   <si>
     <t>插补模式下，使一关节运动到正限位</t>
   </si>
   <si>
-    <t>[165,0,0,0,10,0]</t>
+    <t>[162,0,0,0,10,0]</t>
   </si>
   <si>
     <t>插补模式下，使二关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,-120,90,0,0,10]</t>
+    <t>[0,-114,90,0,0,10]</t>
   </si>
   <si>
     <t>插补模式下，使二关节运动到正限位</t>
   </si>
   <si>
-    <t>[0,120,-90,0,10,0]</t>
+    <t>[0,114,-90,0,10,0]</t>
   </si>
   <si>
     <t>插补模式下，使三关节运动到负限位</t>
   </si>
   <si>
-    <t>[10,0,-158,0,-90,0]</t>
+    <t>[10,0,-154,0,-90,0]</t>
   </si>
   <si>
     <t>插补模式下，使三关节运动到正限位</t>
   </si>
   <si>
-    <t>[-10,0,158,0,90,0]</t>
+    <t>[-10,0,154,0,90,0]</t>
   </si>
   <si>
     <t>插补模式下，使四关节运动到负限位</t>
   </si>
   <si>
-    <t>[10,0,0,-165,-90,0]</t>
+    <t>[10,0,0,-162,-90,0]</t>
   </si>
   <si>
     <t>插补模式下，使四关节运动到正限位</t>
   </si>
   <si>
-    <t>[-10,0,0,165,0,0]</t>
+    <t>[-10,0,0,162,0,0]</t>
   </si>
   <si>
     <t>插补模式下，使五关节运动到负限位</t>
   </si>
   <si>
-    <t>[30,0,0,0,-165,-10]</t>
+    <t>[30,0,0,0,-162,-10]</t>
   </si>
   <si>
     <t>插补模式下，使五关节运动到正限位</t>
   </si>
   <si>
-    <t>[-20,0,0,0,165,30]</t>
+    <t>[-20,0,0,0,162,30]</t>
   </si>
   <si>
     <t>插补模式下，使六关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,30,0,0,0,-175]</t>
+    <t>[0,30,0,0,0,-165]</t>
   </si>
   <si>
     <t>插补模式下，使六关节运动到正限位</t>
   </si>
   <si>
-    <t>[0,-20,0,0,0,175]</t>
+    <t>[0,-20,0,0,0,165]</t>
   </si>
   <si>
     <t>刷新模式下，使一关节运动到负限位</t>
@@ -478,40 +478,40 @@
     <t>全关节运动，角度超限</t>
   </si>
   <si>
-    <t>[-166,0,0,0,0,0]</t>
-  </si>
-  <si>
-    <t>[166,0,0,0,0,0]</t>
-  </si>
-  <si>
-    <t>[0,-121,0,0,0,0]</t>
-  </si>
-  <si>
-    <t>[0,121,0,0,0,0]</t>
-  </si>
-  <si>
-    <t>[0,0,-159,0,0,0]</t>
-  </si>
-  <si>
-    <t>[0,0,159,0,0,0]</t>
-  </si>
-  <si>
-    <t>[0,0,0,-166,0,0]</t>
-  </si>
-  <si>
-    <t>[0,0,0,166,0,0]</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,-166,0]</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,166,0]</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,-176]</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,176]</t>
+    <t>[-163,0,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>[163,0,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>[0,-115,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>[0,115,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>[0,0,-155,0,0,0]</t>
+  </si>
+  <si>
+    <t>[0,0,155,0,0,0]</t>
+  </si>
+  <si>
+    <t>[0,0,0,-163,0,0]</t>
+  </si>
+  <si>
+    <t>[0,0,0,163,0,0]</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,-163,0]</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,163,0]</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,-166]</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,166]</t>
   </si>
   <si>
     <t>全关节运动，速度超限</t>
@@ -736,10 +736,10 @@
     <t>全关节运动，坐标超限，Z轴</t>
   </si>
   <si>
-    <t>[149.9, -86.8, -231, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, 615, 179.99, 0.0, -90.0]</t>
+    <t>[149.9, -86.8, -151, 179.99, 0.0, -90.0]</t>
+  </si>
+  <si>
+    <t>[149.9, -86.8, 677, 179.99, 0.0, -90.0]</t>
   </si>
   <si>
     <t>[149.9, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
@@ -2555,7 +2555,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -2580,7 +2580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="28.8" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2609,17 +2609,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2669,18 +2669,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6296296296296" style="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="40.5" spans="1:8">
+    <row r="4" ht="43.2" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:8">
+    <row r="5" ht="43.2" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2811,18 +2811,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" style="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2901,18 +2901,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2962,17 +2962,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9" style="4"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3158,17 +3158,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="18.25" style="4" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3354,18 +3354,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3415,18 +3415,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3476,18 +3476,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3551,13 +3551,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3630,7 +3630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:7">
+    <row r="4" ht="43.2" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:7">
+    <row r="5" ht="43.2" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:7">
+    <row r="6" ht="43.2" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:7">
+    <row r="7" ht="43.2" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:7">
+    <row r="8" ht="43.2" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:7">
+    <row r="9" ht="43.2" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:7">
+    <row r="10" ht="43.2" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="27" spans="1:7">
+    <row r="11" ht="43.2" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:7">
+    <row r="12" ht="43.2" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="27" spans="1:7">
+    <row r="13" ht="43.2" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="27" spans="1:7">
+    <row r="14" ht="43.2" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:7">
+    <row r="15" ht="43.2" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" ht="27" spans="1:7">
+    <row r="16" ht="43.2" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" ht="27" spans="1:7">
+    <row r="17" ht="43.2" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" ht="27" spans="1:7">
+    <row r="18" ht="43.2" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" ht="27" spans="1:7">
+    <row r="19" ht="43.2" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" ht="27" spans="1:7">
+    <row r="20" ht="43.2" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" ht="27" spans="1:7">
+    <row r="21" ht="43.2" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" ht="27" spans="1:7">
+    <row r="22" ht="43.2" spans="1:7">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" ht="27" spans="1:7">
+    <row r="23" ht="43.2" spans="1:7">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" ht="27" spans="1:7">
+    <row r="24" ht="43.2" spans="1:7">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" ht="27" spans="1:7">
+    <row r="25" ht="43.2" spans="1:7">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" ht="27" spans="1:7">
+    <row r="26" ht="28.8" spans="1:7">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" ht="27" spans="1:7">
+    <row r="27" ht="28.8" spans="1:7">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" ht="27" spans="1:7">
+    <row r="28" ht="28.8" spans="1:7">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" ht="27" spans="1:7">
+    <row r="29" ht="28.8" spans="1:7">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" ht="27" spans="1:7">
+    <row r="30" ht="28.8" spans="1:7">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" ht="27" spans="1:7">
+    <row r="31" ht="28.8" spans="1:7">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" ht="27" spans="1:7">
+    <row r="32" ht="28.8" spans="1:7">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" ht="27" spans="1:7">
+    <row r="33" ht="28.8" spans="1:7">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" ht="27" spans="1:7">
+    <row r="34" ht="28.8" spans="1:7">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" ht="27" spans="1:7">
+    <row r="35" ht="28.8" spans="1:7">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" ht="27" spans="1:7">
+    <row r="36" ht="28.8" spans="1:7">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" ht="27" spans="1:7">
+    <row r="37" ht="28.8" spans="1:7">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" ht="27" spans="1:7">
+    <row r="38" ht="28.8" spans="1:7">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" ht="27" spans="1:7">
+    <row r="39" ht="28.8" spans="1:7">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -4390,7 +4390,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -4415,7 +4415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="28.8" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -4444,14 +4444,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4595,7 +4595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:6">
+    <row r="8" ht="28.8" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:6">
+    <row r="9" ht="28.8" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4639,13 +4639,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4689,7 +4689,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F2" s="1">
         <v>30</v>
@@ -4715,7 +4715,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F3" s="1">
         <v>50</v>
@@ -4727,7 +4727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>-120</v>
+        <v>-114</v>
       </c>
       <c r="F4" s="1">
         <v>70</v>
@@ -4753,7 +4753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F5" s="1">
         <v>20</v>
@@ -4779,7 +4779,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>-158</v>
+        <v>-154</v>
       </c>
       <c r="F6" s="1">
         <v>30</v>
@@ -4805,7 +4805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F7" s="1">
         <v>30</v>
@@ -4831,7 +4831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F8" s="1">
         <v>40</v>
@@ -4857,7 +4857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F9" s="1">
         <v>40</v>
@@ -4883,7 +4883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F10" s="1">
         <v>50</v>
@@ -4909,7 +4909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F11" s="1">
         <v>50</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="1">
-        <v>-175</v>
+        <v>-165</v>
       </c>
       <c r="F12" s="1">
         <v>60</v>
@@ -4961,7 +4961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F13" s="1">
         <v>60</v>
@@ -4987,7 +4987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F14" s="1">
         <v>20</v>
@@ -5013,7 +5013,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F15" s="1">
         <v>50</v>
@@ -5039,7 +5039,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1">
-        <v>-120</v>
+        <v>-114</v>
       </c>
       <c r="F16" s="1">
         <v>20</v>
@@ -5065,7 +5065,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="1">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F17" s="1">
         <v>20</v>
@@ -5091,7 +5091,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="1">
-        <v>-158</v>
+        <v>-154</v>
       </c>
       <c r="F18" s="1">
         <v>30</v>
@@ -5117,7 +5117,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="1">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F19" s="1">
         <v>30</v>
@@ -5143,7 +5143,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F20" s="1">
         <v>40</v>
@@ -5169,7 +5169,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F21" s="1">
         <v>40</v>
@@ -5195,7 +5195,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F22" s="1">
         <v>50</v>
@@ -5221,7 +5221,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F23" s="1">
         <v>50</v>
@@ -5247,7 +5247,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>6</v>
       </c>
       <c r="E24" s="1">
-        <v>-175</v>
+        <v>-165</v>
       </c>
       <c r="F24" s="1">
         <v>100</v>
@@ -5273,7 +5273,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
@@ -5299,7 +5299,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="F26" s="1">
         <v>50</v>
@@ -5322,7 +5322,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="1">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F27" s="1">
         <v>50</v>
@@ -5345,7 +5345,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="1">
-        <v>-121</v>
+        <v>-115</v>
       </c>
       <c r="F28" s="1">
         <v>50</v>
@@ -5368,7 +5368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="1">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F29" s="1">
         <v>50</v>
@@ -5391,7 +5391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="1">
-        <v>-159</v>
+        <v>-155</v>
       </c>
       <c r="F30" s="1">
         <v>50</v>
@@ -5414,7 +5414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="1">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F31" s="1">
         <v>50</v>
@@ -5437,7 +5437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="32" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="F32" s="1">
         <v>50</v>
@@ -5460,7 +5460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="33" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F33" s="1">
         <v>50</v>
@@ -5483,7 +5483,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="34" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>5</v>
       </c>
       <c r="E34" s="1">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="F34" s="1">
         <v>50</v>
@@ -5506,7 +5506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="35" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="1">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F35" s="1">
         <v>50</v>
@@ -5529,7 +5529,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="36" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="1">
-        <v>-176</v>
+        <v>-166</v>
       </c>
       <c r="F36" s="1">
         <v>50</v>
@@ -5552,7 +5552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="37" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="1">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F37" s="1">
         <v>50</v>
@@ -5631,14 +5631,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.3796296296296" style="1" customWidth="1"/>
     <col min="5" max="5" width="50" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5794,13 +5794,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5873,7 +5873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="32" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -6501,7 +6501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="33" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -6531,14 +6531,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.625" style="1" customWidth="1"/>
-    <col min="6" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1296296296296" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -6620,7 +6620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -7166,7 +7166,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="1">
-        <v>-231</v>
+        <v>-151</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>22</v>
@@ -7306,7 +7306,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="1">
-        <v>615</v>
+        <v>678</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>22</v>
@@ -7368,18 +7368,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7483,18 +7483,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7564,18 +7564,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7623,18 +7623,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7738,15 +7738,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="49.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7842,7 +7842,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -7915,7 +7915,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -7940,7 +7940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="28.8" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -7969,18 +7969,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="22.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8046,16 +8046,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.5583333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -8146,7 +8146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -8204,7 +8204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -8465,7 +8465,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -8610,7 +8610,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -8639,7 +8639,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:9">
+    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:9">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -8952,15 +8952,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5583333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -9042,7 +9042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -9146,7 +9146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A8" s="2">
         <v>13</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A9" s="2">
         <v>14</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A10" s="2">
         <v>15</v>
       </c>
@@ -9224,7 +9224,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A11" s="2">
         <v>16</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A12" s="2">
         <v>17</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A13" s="2">
         <v>18</v>
       </c>
@@ -9456,15 +9456,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5583333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -9546,7 +9546,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -9806,7 +9806,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -10066,7 +10066,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -10272,15 +10272,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5583333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -10362,7 +10362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -10440,7 +10440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -10466,7 +10466,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -10726,7 +10726,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -10830,7 +10830,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="40.5" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -10908,7 +10908,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -11088,15 +11088,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5583333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -11178,7 +11178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -11230,7 +11230,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -11308,7 +11308,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -11464,7 +11464,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -11750,7 +11750,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -11846,7 +11846,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="27" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -11904,14 +11904,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12019,14 +12019,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12229,14 +12229,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12344,14 +12344,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12554,7 +12554,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -12579,7 +12579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
+    <row r="2" ht="28.8" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -12607,14 +12607,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12652,7 +12652,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -12672,13 +12672,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>-120</v>
+        <v>-114</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12692,13 +12692,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>-158</v>
+        <v>-154</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12712,13 +12712,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:6">
+    <row r="6" ht="28.8" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -12732,13 +12732,13 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:6">
+    <row r="7" ht="28.8" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -12752,13 +12752,13 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>-175</v>
+        <v>-165</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:6">
+    <row r="8" ht="28.8" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:6">
+    <row r="9" ht="28.8" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -12802,14 +12802,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -12882,7 +12882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -12905,7 +12905,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12928,7 +12928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -12951,7 +12951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -12997,7 +12997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>-110</v>
+        <v>-100</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -13020,7 +13020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -13034,7 +13034,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="1">
-        <v>-150</v>
+        <v>-140</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -13043,7 +13043,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -13112,7 +13112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -13152,7 +13152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" ht="27" spans="1:7">
+    <row r="16" ht="28.8" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -13166,13 +13166,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="1">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="27" spans="1:7">
+    <row r="17" ht="28.8" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -13186,13 +13186,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="1">
-        <v>-121</v>
+        <v>-115</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="27" spans="1:7">
+    <row r="18" ht="28.8" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -13206,13 +13206,13 @@
         <v>3</v>
       </c>
       <c r="E18" s="1">
-        <v>-159</v>
+        <v>-155</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="27" spans="1:7">
+    <row r="19" ht="28.8" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -13226,13 +13226,13 @@
         <v>4</v>
       </c>
       <c r="E19" s="1">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" ht="27" spans="1:7">
+    <row r="20" ht="28.8" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -13246,13 +13246,13 @@
         <v>5</v>
       </c>
       <c r="E20" s="1">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" ht="27" spans="1:7">
+    <row r="21" ht="28.8" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>-176</v>
+        <v>-166</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>22</v>
@@ -13282,14 +13282,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -13327,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -13347,13 +13347,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -13367,13 +13367,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -13387,13 +13387,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -13407,13 +13407,13 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -13427,13 +13427,13 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -13450,7 +13450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -13477,14 +13477,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -13525,7 +13525,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -13557,7 +13557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -13594,7 +13594,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -13603,7 +13603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -13617,7 +13617,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -13626,7 +13626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -13649,7 +13649,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -13672,7 +13672,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -13686,7 +13686,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -13695,7 +13695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -13709,7 +13709,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="1">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -13741,7 +13741,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -13764,7 +13764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -13807,7 +13807,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -13841,13 +13841,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="1">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -13861,13 +13861,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="1">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -13881,13 +13881,13 @@
         <v>3</v>
       </c>
       <c r="E18" s="1">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -13901,13 +13901,13 @@
         <v>4</v>
       </c>
       <c r="E19" s="1">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -13921,13 +13921,13 @@
         <v>5</v>
       </c>
       <c r="E20" s="1">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>22</v>
@@ -13957,13 +13957,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -14013,14 +14013,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -14084,7 +14084,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -14164,7 +14164,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -14208,14 +14208,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -14608,13 +14608,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -14664,7 +14664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:7">
+    <row r="3" ht="28.8" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -14687,7 +14687,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:7">
+    <row r="4" ht="28.8" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:7">
+    <row r="5" ht="28.8" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -14733,7 +14733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:7">
+    <row r="6" ht="28.8" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:7">
+    <row r="7" ht="28.8" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:7">
+    <row r="8" ht="28.8" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:7">
+    <row r="9" ht="28.8" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:7">
+    <row r="10" ht="28.8" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -14848,7 +14848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="27" spans="1:7">
+    <row r="11" ht="28.8" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:7">
+    <row r="12" ht="28.8" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="27" spans="1:7">
+    <row r="13" ht="28.8" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -15053,13 +15053,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15107,14 +15107,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15156,7 +15156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="28.8" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -15186,7 +15186,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -15211,7 +15211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="28.8" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -15239,14 +15239,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15288,7 +15288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -15318,14 +15318,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -15377,12 +15377,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16051,13 +16051,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16107,7 +16107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -16130,7 +16130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -16153,7 +16153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -16176,7 +16176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A6" s="2">
         <v>25</v>
       </c>
@@ -16196,7 +16196,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A7" s="2">
         <v>26</v>
       </c>
@@ -16216,7 +16216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A8" s="2">
         <v>27</v>
       </c>
@@ -16236,7 +16236,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="27" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
       <c r="A9" s="2">
         <v>28</v>
       </c>
@@ -16266,12 +16266,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16379,13 +16379,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16560,12 +16560,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16873,14 +16873,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16932,13 +16932,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -16992,14 +16992,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17051,17 +17051,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9" style="4"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17121,7 +17121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -17139,7 +17139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -17167,13 +17167,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17281,14 +17281,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17340,13 +17340,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17516,14 +17516,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17575,13 +17575,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17691,14 +17691,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17750,14 +17750,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17809,13 +17809,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.25" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -17925,14 +17925,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18023,14 +18023,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18090,17 +18090,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18150,14 +18150,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -18201,7 +18201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -18221,7 +18221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -18241,7 +18241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -18278,7 +18278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -18310,7 +18310,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -18321,7 +18321,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -18332,17 +18332,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9" style="4"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18522,7 +18522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:6">
+    <row r="10" ht="28.8" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -18539,7 +18539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" ht="27" spans="1:6">
+    <row r="11" ht="28.8" spans="1:6">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -18566,17 +18566,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="22" activeTab="22"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="62" activeTab="67"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="516">
   <si>
     <t>ID</t>
   </si>
@@ -835,6 +835,9 @@
     <t>jog_angle</t>
   </si>
   <si>
+    <t>错误：刷新模式无法使用JOG运动，请切换插补模式使用</t>
+  </si>
+  <si>
     <t>设置关节超限</t>
   </si>
   <si>
@@ -1288,49 +1291,91 @@
     <t>设置开关状态超限</t>
   </si>
   <si>
-    <t>设置1关节力矩状态，掉使能</t>
+    <t>插补模式设置1关节力矩状态，掉使能</t>
   </si>
   <si>
     <t>set_motor_enabled</t>
   </si>
   <si>
-    <t>设置1关节力矩状态，上使能</t>
-  </si>
-  <si>
-    <t>设置2关节力矩状态，掉使能</t>
-  </si>
-  <si>
-    <t>设置2关节力矩状态，上使能</t>
-  </si>
-  <si>
-    <t>设置3关节力矩状态，掉使能</t>
-  </si>
-  <si>
-    <t>设置3关节力矩状态，上使能</t>
-  </si>
-  <si>
-    <t>设置4关节力矩状态，掉使能</t>
-  </si>
-  <si>
-    <t>设置4关节力矩状态，上使能</t>
-  </si>
-  <si>
-    <t>设置5关节力矩状态，掉使能</t>
-  </si>
-  <si>
-    <t>设置5关节力矩状态，上使能</t>
-  </si>
-  <si>
-    <t>设置6关节力矩状态，掉使能</t>
-  </si>
-  <si>
-    <t>设置6关节力矩状态，上使能</t>
-  </si>
-  <si>
-    <t>设置全关节掉使能</t>
-  </si>
-  <si>
-    <t>设置全关节上使能</t>
+    <t>插补模式设置1关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>插补模式设置2关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>插补模式设置2关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>插补模式设置3关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>插补模式设置3关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>插补模式设置4关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>插补模式设置4关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>插补模式设置5关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>插补模式设置5关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>插补模式设置6关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>插补模式设置6关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>插补模式设置全关节掉使能</t>
+  </si>
+  <si>
+    <t>插补模式设置全关节上使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置1关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置1关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置2关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置2关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置3关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置3关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置4关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置4关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置5关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置5关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置6关节力矩状态，掉使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置6关节力矩状态，上使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置全关节掉使能</t>
+  </si>
+  <si>
+    <t>刷新模式设置全关节上使能</t>
   </si>
   <si>
     <t>读取零位编码器值</t>
@@ -4427,7 +4472,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="7">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -7952,7 +7997,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -8105,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -8134,7 +8179,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G3" s="2">
         <v>50</v>
@@ -8163,7 +8208,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>-120</v>
+        <v>-114</v>
       </c>
       <c r="G4" s="2">
         <v>70</v>
@@ -8192,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G5" s="2">
         <v>20</v>
@@ -8221,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>-158</v>
+        <v>-154</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -8250,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -8279,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="G8" s="2">
         <v>40</v>
@@ -8308,7 +8353,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G9" s="2">
         <v>40</v>
@@ -8337,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="G10" s="2">
         <v>50</v>
@@ -8366,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G11" s="2">
         <v>50</v>
@@ -8395,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="2">
-        <v>-175</v>
+        <v>-165</v>
       </c>
       <c r="G12" s="2">
         <v>60</v>
@@ -8424,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G13" s="2">
         <v>60</v>
@@ -8436,7 +8481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -8452,20 +8497,18 @@
       <c r="E14" s="2">
         <v>0</v>
       </c>
-      <c r="F14" s="2">
-        <v>-165</v>
-      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2">
         <v>20</v>
       </c>
-      <c r="H14" s="2">
-        <v>1</v>
+      <c r="H14" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="15" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -8481,20 +8524,18 @@
       <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="F15" s="2">
-        <v>165</v>
-      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="2">
         <v>50</v>
       </c>
-      <c r="H15" s="2">
-        <v>1</v>
+      <c r="H15" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -8510,20 +8551,18 @@
       <c r="E16" s="2">
         <v>0</v>
       </c>
-      <c r="F16" s="2">
-        <v>-120</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2">
         <v>20</v>
       </c>
-      <c r="H16" s="2">
-        <v>1</v>
+      <c r="H16" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="17" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -8539,20 +8578,18 @@
       <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="F17" s="2">
-        <v>120</v>
-      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2">
         <v>20</v>
       </c>
-      <c r="H17" s="2">
-        <v>1</v>
+      <c r="H17" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="18" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -8568,20 +8605,18 @@
       <c r="E18" s="2">
         <v>0</v>
       </c>
-      <c r="F18" s="2">
-        <v>-158</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2">
         <v>30</v>
       </c>
-      <c r="H18" s="2">
-        <v>1</v>
+      <c r="H18" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="19" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -8597,20 +8632,18 @@
       <c r="E19" s="2">
         <v>1</v>
       </c>
-      <c r="F19" s="2">
-        <v>158</v>
-      </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="2">
         <v>30</v>
       </c>
-      <c r="H19" s="2">
-        <v>1</v>
+      <c r="H19" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="20" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -8626,20 +8659,18 @@
       <c r="E20" s="2">
         <v>0</v>
       </c>
-      <c r="F20" s="2">
-        <v>-165</v>
-      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2">
         <v>40</v>
       </c>
-      <c r="H20" s="2">
-        <v>1</v>
+      <c r="H20" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="21" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -8655,20 +8686,18 @@
       <c r="E21" s="2">
         <v>1</v>
       </c>
-      <c r="F21" s="2">
-        <v>165</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2">
         <v>40</v>
       </c>
-      <c r="H21" s="2">
-        <v>1</v>
+      <c r="H21" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="22" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -8684,20 +8713,18 @@
       <c r="E22" s="2">
         <v>0</v>
       </c>
-      <c r="F22" s="2">
-        <v>-165</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2">
         <v>50</v>
       </c>
-      <c r="H22" s="2">
-        <v>1</v>
+      <c r="H22" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="23" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -8713,20 +8740,18 @@
       <c r="E23" s="2">
         <v>1</v>
       </c>
-      <c r="F23" s="2">
-        <v>165</v>
-      </c>
+      <c r="F23" s="2"/>
       <c r="G23" s="2">
         <v>50</v>
       </c>
-      <c r="H23" s="2">
-        <v>1</v>
+      <c r="H23" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="24" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -8742,20 +8767,18 @@
       <c r="E24" s="2">
         <v>0</v>
       </c>
-      <c r="F24" s="2">
-        <v>-175</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2">
         <v>100</v>
       </c>
-      <c r="H24" s="2">
-        <v>1</v>
+      <c r="H24" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:9">
+    <row r="25" s="1" customFormat="1" ht="72" spans="1:9">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -8769,16 +8792,14 @@
         <v>6</v>
       </c>
       <c r="E25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2">
-        <v>175</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2">
         <v>100</v>
       </c>
-      <c r="H25" s="2">
-        <v>1</v>
+      <c r="H25" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>53</v>
@@ -8843,7 +8864,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>244</v>
@@ -8869,7 +8890,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>244</v>
@@ -8895,7 +8916,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>244</v>
@@ -8921,7 +8942,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>244</v>
@@ -8995,10 +9016,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -9021,10 +9042,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -9047,10 +9068,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -9073,10 +9094,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -9099,10 +9120,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -9125,10 +9146,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -9146,15 +9167,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A8" s="2">
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -9165,22 +9186,22 @@
       <c r="F8" s="2">
         <v>20</v>
       </c>
-      <c r="G8" s="2">
-        <v>1</v>
+      <c r="G8" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A9" s="2">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -9191,22 +9212,22 @@
       <c r="F9" s="2">
         <v>50</v>
       </c>
-      <c r="G9" s="2">
-        <v>1</v>
+      <c r="G9" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A10" s="2">
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -9217,22 +9238,22 @@
       <c r="F10" s="2">
         <v>20</v>
       </c>
-      <c r="G10" s="2">
-        <v>1</v>
+      <c r="G10" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A11" s="2">
         <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -9243,22 +9264,22 @@
       <c r="F11" s="2">
         <v>20</v>
       </c>
-      <c r="G11" s="2">
-        <v>1</v>
+      <c r="G11" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A12" s="2">
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -9269,22 +9290,22 @@
       <c r="F12" s="2">
         <v>30</v>
       </c>
-      <c r="G12" s="2">
-        <v>1</v>
+      <c r="G12" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A13" s="2">
         <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -9295,8 +9316,8 @@
       <c r="F13" s="2">
         <v>30</v>
       </c>
-      <c r="G13" s="2">
-        <v>1</v>
+      <c r="G13" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>53</v>
@@ -9310,7 +9331,7 @@
         <v>155</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -9334,7 +9355,7 @@
         <v>155</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -9355,10 +9376,10 @@
         <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -9379,10 +9400,10 @@
         <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -9403,10 +9424,10 @@
         <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -9427,10 +9448,10 @@
         <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D19" s="2">
         <v>4</v>
@@ -9499,10 +9520,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -9525,10 +9546,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -9551,10 +9572,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -9577,10 +9598,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -9603,10 +9624,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -9621,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -9629,10 +9650,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -9655,10 +9676,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -9681,10 +9702,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -9707,10 +9728,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -9733,10 +9754,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -9759,10 +9780,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -9785,10 +9806,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -9806,15 +9827,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -9825,22 +9846,22 @@
       <c r="F14" s="2">
         <v>20</v>
       </c>
-      <c r="G14" s="2">
-        <v>-1</v>
+      <c r="G14" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -9851,22 +9872,22 @@
       <c r="F15" s="2">
         <v>50</v>
       </c>
-      <c r="G15" s="2">
-        <v>-1</v>
+      <c r="G15" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -9877,22 +9898,22 @@
       <c r="F16" s="2">
         <v>20</v>
       </c>
-      <c r="G16" s="2">
-        <v>-1</v>
+      <c r="G16" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -9903,22 +9924,22 @@
       <c r="F17" s="2">
         <v>20</v>
       </c>
-      <c r="G17" s="2">
-        <v>-1</v>
+      <c r="G17" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -9929,22 +9950,22 @@
       <c r="F18" s="2">
         <v>30</v>
       </c>
-      <c r="G18" s="2">
-        <v>-1</v>
+      <c r="G18" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -9955,22 +9976,22 @@
       <c r="F19" s="2">
         <v>30</v>
       </c>
-      <c r="G19" s="2">
-        <v>-1</v>
+      <c r="G19" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -9981,22 +10002,22 @@
       <c r="F20" s="2">
         <v>40</v>
       </c>
-      <c r="G20" s="2">
-        <v>-1</v>
+      <c r="G20" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -10007,22 +10028,22 @@
       <c r="F21" s="2">
         <v>40</v>
       </c>
-      <c r="G21" s="2">
-        <v>-1</v>
+      <c r="G21" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -10033,22 +10054,22 @@
       <c r="F22" s="2">
         <v>50</v>
       </c>
-      <c r="G22" s="2">
-        <v>-1</v>
+      <c r="G22" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -10059,22 +10080,22 @@
       <c r="F23" s="2">
         <v>50</v>
       </c>
-      <c r="G23" s="2">
-        <v>-1</v>
+      <c r="G23" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -10085,22 +10106,22 @@
       <c r="F24" s="2">
         <v>100</v>
       </c>
-      <c r="G24" s="2">
-        <v>-1</v>
+      <c r="G24" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -10111,8 +10132,8 @@
       <c r="F25" s="2">
         <v>100</v>
       </c>
-      <c r="G25" s="2">
-        <v>-1</v>
+      <c r="G25" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -10126,7 +10147,7 @@
         <v>155</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -10150,7 +10171,7 @@
         <v>155</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -10171,10 +10192,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -10195,10 +10216,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -10219,10 +10240,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -10243,10 +10264,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
@@ -10298,7 +10319,7 @@
         <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -10315,10 +10336,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -10341,10 +10362,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -10367,10 +10388,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -10393,10 +10414,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -10419,10 +10440,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -10445,10 +10466,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -10471,10 +10492,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -10497,10 +10518,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -10523,10 +10544,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -10549,10 +10570,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -10575,10 +10596,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -10601,10 +10622,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -10622,15 +10643,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -10641,22 +10662,22 @@
       <c r="F14" s="2">
         <v>20</v>
       </c>
-      <c r="G14" s="2">
-        <v>0</v>
+      <c r="G14" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -10667,22 +10688,22 @@
       <c r="F15" s="2">
         <v>50</v>
       </c>
-      <c r="G15" s="2">
-        <v>-1</v>
+      <c r="G15" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -10693,22 +10714,22 @@
       <c r="F16" s="2">
         <v>20</v>
       </c>
-      <c r="G16" s="2">
-        <v>-1</v>
+      <c r="G16" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -10719,22 +10740,22 @@
       <c r="F17" s="2">
         <v>20</v>
       </c>
-      <c r="G17" s="2">
-        <v>-1</v>
+      <c r="G17" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -10745,22 +10766,22 @@
       <c r="F18" s="2">
         <v>30</v>
       </c>
-      <c r="G18" s="2">
-        <v>-1</v>
+      <c r="G18" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -10771,22 +10792,22 @@
       <c r="F19" s="2">
         <v>30</v>
       </c>
-      <c r="G19" s="2">
-        <v>-1</v>
+      <c r="G19" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -10797,22 +10818,22 @@
       <c r="F20" s="2">
         <v>40</v>
       </c>
-      <c r="G20" s="2">
-        <v>-1</v>
+      <c r="G20" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -10823,22 +10844,22 @@
       <c r="F21" s="2">
         <v>40</v>
       </c>
-      <c r="G21" s="2">
-        <v>-1</v>
+      <c r="G21" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -10849,22 +10870,22 @@
       <c r="F22" s="2">
         <v>50</v>
       </c>
-      <c r="G22" s="2">
-        <v>-1</v>
+      <c r="G22" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -10875,22 +10896,22 @@
       <c r="F23" s="2">
         <v>50</v>
       </c>
-      <c r="G23" s="2">
-        <v>-1</v>
+      <c r="G23" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -10901,22 +10922,22 @@
       <c r="F24" s="2">
         <v>100</v>
       </c>
-      <c r="G24" s="2">
-        <v>-1</v>
+      <c r="G24" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -10927,8 +10948,8 @@
       <c r="F25" s="2">
         <v>100</v>
       </c>
-      <c r="G25" s="2">
-        <v>-1</v>
+      <c r="G25" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -10942,7 +10963,7 @@
         <v>155</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -10966,7 +10987,7 @@
         <v>155</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -10987,10 +11008,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -11011,10 +11032,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -11035,10 +11056,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -11059,10 +11080,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -11114,7 +11135,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>87</v>
@@ -11131,10 +11152,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -11157,10 +11178,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -11183,10 +11204,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -11209,10 +11230,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -11235,10 +11256,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -11261,10 +11282,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -11287,10 +11308,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -11313,10 +11334,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -11339,10 +11360,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -11365,10 +11386,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -11391,10 +11412,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -11417,10 +11438,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -11438,15 +11459,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -11457,22 +11478,22 @@
       <c r="F14" s="2">
         <v>20</v>
       </c>
-      <c r="G14" s="2">
-        <v>-1</v>
+      <c r="G14" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -11483,22 +11504,22 @@
       <c r="F15" s="2">
         <v>50</v>
       </c>
-      <c r="G15" s="2">
-        <v>-1</v>
+      <c r="G15" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -11509,22 +11530,22 @@
       <c r="F16" s="2">
         <v>20</v>
       </c>
-      <c r="G16" s="2">
-        <v>-1</v>
+      <c r="G16" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -11535,22 +11556,22 @@
       <c r="F17" s="2">
         <v>20</v>
       </c>
-      <c r="G17" s="2">
-        <v>-1</v>
+      <c r="G17" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -11561,22 +11582,22 @@
       <c r="F18" s="2">
         <v>30</v>
       </c>
-      <c r="G18" s="2">
-        <v>-1</v>
+      <c r="G18" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -11587,22 +11608,22 @@
       <c r="F19" s="2">
         <v>30</v>
       </c>
-      <c r="G19" s="2">
-        <v>-1</v>
+      <c r="G19" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -11613,22 +11634,22 @@
       <c r="F20" s="2">
         <v>40</v>
       </c>
-      <c r="G20" s="2">
-        <v>-1</v>
+      <c r="G20" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -11639,22 +11660,22 @@
       <c r="F21" s="2">
         <v>40</v>
       </c>
-      <c r="G21" s="2">
-        <v>-1</v>
+      <c r="G21" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -11665,22 +11686,22 @@
       <c r="F22" s="2">
         <v>50</v>
       </c>
-      <c r="G22" s="2">
-        <v>-1</v>
+      <c r="G22" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -11691,22 +11712,22 @@
       <c r="F23" s="2">
         <v>50</v>
       </c>
-      <c r="G23" s="2">
-        <v>-1</v>
+      <c r="G23" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -11717,22 +11738,22 @@
       <c r="F24" s="2">
         <v>100</v>
       </c>
-      <c r="G24" s="2">
-        <v>-1</v>
+      <c r="G24" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="72" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -11743,8 +11764,8 @@
       <c r="F25" s="2">
         <v>100</v>
       </c>
-      <c r="G25" s="2">
-        <v>-1</v>
+      <c r="G25" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>53</v>
@@ -11758,7 +11779,7 @@
         <v>155</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -11782,7 +11803,7 @@
         <v>155</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -11803,10 +11824,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -11827,10 +11848,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -11851,10 +11872,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -11875,10 +11896,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -11940,10 +11961,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -11960,10 +11981,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -11983,7 +12004,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12000,7 +12021,7 @@
         <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -12058,10 +12079,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12081,10 +12102,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12107,7 +12128,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12127,7 +12148,7 @@
         <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -12147,7 +12168,7 @@
         <v>224</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -12167,7 +12188,7 @@
         <v>224</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -12184,10 +12205,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -12204,10 +12225,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -12265,10 +12286,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12285,10 +12306,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12308,7 +12329,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -12325,7 +12346,7 @@
         <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -12383,10 +12404,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -12406,10 +12427,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -12432,7 +12453,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -12452,7 +12473,7 @@
         <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -12472,7 +12493,7 @@
         <v>224</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -12492,7 +12513,7 @@
         <v>224</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -12509,10 +12530,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -12529,10 +12550,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -12643,10 +12664,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12663,10 +12684,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12683,10 +12704,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12703,10 +12724,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12723,10 +12744,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12743,10 +12764,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12763,10 +12784,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -12780,10 +12801,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -12841,10 +12862,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -12864,10 +12885,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -12887,10 +12908,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -12910,10 +12931,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -12933,10 +12954,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -12956,10 +12977,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -12979,10 +13000,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -13002,10 +13023,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -13025,10 +13046,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -13048,10 +13069,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -13071,10 +13092,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -13094,10 +13115,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13117,10 +13138,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -13137,10 +13158,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13160,7 +13181,7 @@
         <v>149</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13180,7 +13201,7 @@
         <v>150</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -13200,7 +13221,7 @@
         <v>151</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -13220,7 +13241,7 @@
         <v>152</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
@@ -13240,7 +13261,7 @@
         <v>153</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D20" s="1">
         <v>5</v>
@@ -13260,7 +13281,7 @@
         <v>154</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -13318,10 +13339,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13338,10 +13359,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13358,10 +13379,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13378,10 +13399,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13398,10 +13419,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13418,10 +13439,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13438,10 +13459,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -13455,10 +13476,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -13516,10 +13537,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -13539,10 +13560,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -13562,10 +13583,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -13585,10 +13606,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -13608,10 +13629,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -13631,10 +13652,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -13654,10 +13675,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -13677,10 +13698,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -13700,10 +13721,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -13723,10 +13744,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -13746,10 +13767,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -13769,10 +13790,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -13792,10 +13813,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -13812,10 +13833,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -13835,7 +13856,7 @@
         <v>149</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -13855,7 +13876,7 @@
         <v>150</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -13875,7 +13896,7 @@
         <v>151</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -13895,7 +13916,7 @@
         <v>152</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
@@ -13915,7 +13936,7 @@
         <v>153</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D20" s="1">
         <v>5</v>
@@ -13935,7 +13956,7 @@
         <v>154</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D21" s="1">
         <v>6</v>
@@ -13992,10 +14013,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -14049,10 +14070,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14069,10 +14090,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -14089,10 +14110,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -14109,10 +14130,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -14129,10 +14150,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -14149,10 +14170,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -14169,10 +14190,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -14186,10 +14207,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -14247,10 +14268,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14270,10 +14291,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14293,10 +14314,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14316,10 +14337,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14339,10 +14360,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14362,10 +14383,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14385,10 +14406,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14408,10 +14429,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14431,10 +14452,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14454,10 +14475,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14477,10 +14498,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14500,10 +14521,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14523,10 +14544,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -14543,10 +14564,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -14563,10 +14584,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -14583,10 +14604,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -14607,7 +14628,7 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -14646,10 +14667,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -14669,10 +14690,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -14692,10 +14713,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -14715,10 +14736,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -14738,10 +14759,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -14761,10 +14782,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -14784,10 +14805,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -14807,10 +14828,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -14830,10 +14851,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -14853,10 +14874,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -14876,10 +14897,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -14899,10 +14920,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -14917,15 +14938,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" ht="28.8" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D14" s="1">
         <v>254</v>
@@ -14940,15 +14961,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" ht="28.8" spans="1:7">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D15" s="1">
         <v>254</v>
@@ -14963,83 +14984,405 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" ht="28.8" spans="1:7">
       <c r="A16" s="2">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:7">
+      <c r="A17" s="2">
+        <v>2</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" ht="28.8" spans="1:7">
+      <c r="A18" s="2">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" ht="28.8" spans="1:7">
+      <c r="A19" s="2">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:7">
+      <c r="A20" s="2">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" spans="1:7">
+      <c r="A21" s="2">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:7">
+      <c r="A22" s="2">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D22" s="1">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" ht="28.8" spans="1:7">
+      <c r="A23" s="2">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" ht="28.8" spans="1:7">
+      <c r="A24" s="2">
+        <v>9</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" ht="28.8" spans="1:7">
+      <c r="A25" s="2">
+        <v>10</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D25" s="1">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" ht="28.8" spans="1:7">
+      <c r="A26" s="2">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" ht="28.8" spans="1:7">
+      <c r="A27" s="2">
+        <v>12</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D27" s="1">
+        <v>6</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" ht="28.8" spans="1:7">
+      <c r="A28" s="2">
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D28" s="1">
+        <v>254</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" ht="28.8" spans="1:7">
+      <c r="A29" s="2">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D29" s="1">
+        <v>254</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2">
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="B31" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D31" s="1">
         <v>7</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2">
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2">
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="B33" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D33" s="1">
         <v>4</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E33" s="1">
         <v>255</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -15088,10 +15431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15143,14 +15486,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15161,16 +15504,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="D3" s="2">
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -15275,14 +15618,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15293,16 +15636,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="D3" s="2">
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>53</v>
@@ -15354,14 +15697,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -15397,10 +15740,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -15414,10 +15757,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -15437,10 +15780,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -15460,10 +15803,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -15483,10 +15826,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -15506,10 +15849,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -15529,10 +15872,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -15552,10 +15895,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -15575,10 +15918,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -15598,10 +15941,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -15621,10 +15964,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -15644,10 +15987,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -15667,10 +16010,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -15690,10 +16033,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -15713,10 +16056,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -15736,10 +16079,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D16" s="1">
         <v>8</v>
@@ -15759,10 +16102,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D17" s="1">
         <v>8</v>
@@ -15782,10 +16125,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D18" s="1">
         <v>9</v>
@@ -15805,10 +16148,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D19" s="1">
         <v>9</v>
@@ -15828,10 +16171,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
@@ -15851,10 +16194,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D21" s="1">
         <v>10</v>
@@ -15874,10 +16217,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D22" s="1">
         <v>11</v>
@@ -15897,10 +16240,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D23" s="1">
         <v>11</v>
@@ -15920,10 +16263,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D24" s="1">
         <v>12</v>
@@ -15943,10 +16286,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D25" s="1">
         <v>12</v>
@@ -15966,10 +16309,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
@@ -15986,10 +16329,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -16006,10 +16349,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -16026,10 +16369,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -16072,10 +16415,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -16089,10 +16432,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16112,10 +16455,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16135,10 +16478,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -16158,10 +16501,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -16181,10 +16524,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -16201,10 +16544,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -16221,10 +16564,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -16241,10 +16584,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -16286,7 +16629,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -16300,10 +16643,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16320,10 +16663,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16340,10 +16683,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16357,10 +16700,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -16417,16 +16760,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -16440,16 +16783,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -16463,16 +16806,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -16486,16 +16829,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -16509,16 +16852,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -16532,16 +16875,16 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -16580,7 +16923,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -16594,10 +16937,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16614,10 +16957,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16634,10 +16977,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16654,10 +16997,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -16674,10 +17017,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -16694,10 +17037,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -16714,10 +17057,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -16734,10 +17077,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -16754,10 +17097,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
@@ -16774,10 +17117,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
@@ -16794,10 +17137,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D12" s="1">
         <v>11</v>
@@ -16814,10 +17157,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
@@ -16834,10 +17177,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
@@ -16851,10 +17194,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -16909,14 +17252,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -16967,13 +17310,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -17028,14 +17371,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -17202,10 +17545,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -17222,10 +17565,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -17245,7 +17588,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -17262,7 +17605,7 @@
         <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -17317,10 +17660,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1">
@@ -17375,10 +17718,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -17395,10 +17738,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -17415,10 +17758,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -17435,10 +17778,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
@@ -17455,10 +17798,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D6" s="2">
         <v>4</v>
@@ -17478,7 +17821,7 @@
         <v>224</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -17496,7 +17839,7 @@
         <v>224</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D8" s="2">
         <v>-1</v>
@@ -17552,10 +17895,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1">
@@ -17610,10 +17953,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -17630,10 +17973,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -17653,7 +17996,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -17671,7 +18014,7 @@
         <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -17727,10 +18070,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -17786,10 +18129,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -17844,10 +18187,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -17864,10 +18207,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -17887,7 +18230,7 @@
         <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -17905,7 +18248,7 @@
         <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="D5" s="2">
         <v>-1</v>
@@ -17947,7 +18290,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -17961,16 +18304,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="D2" s="2">
         <v>5</v>
       </c>
       <c r="E2" s="2">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -17981,10 +18324,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -17998,10 +18341,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="D4" s="2">
         <v>6</v>
@@ -18045,10 +18388,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -18062,10 +18405,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="D2" s="2">
         <v>5</v>
@@ -18172,7 +18515,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -18186,10 +18529,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -18206,10 +18549,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
@@ -18226,10 +18569,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -18246,10 +18589,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
@@ -18266,10 +18609,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -18283,10 +18626,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="38" activeTab="42"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -11199,7 +11199,6 @@
       <c r="F32" s="2">
         <v>50</v>
       </c>
-      <c r="G32" s="2"/>
       <c r="H32" s="1" t="s">
         <v>23</v>
       </c>
@@ -11223,7 +11222,6 @@
       <c r="F33" s="2">
         <v>50</v>
       </c>
-      <c r="G33" s="2"/>
       <c r="H33" s="1" t="s">
         <v>23</v>
       </c>
@@ -11247,7 +11245,6 @@
       <c r="F34" s="2">
         <v>50</v>
       </c>
-      <c r="G34" s="2"/>
       <c r="H34" s="1" t="s">
         <v>23</v>
       </c>
@@ -11271,7 +11268,6 @@
       <c r="F35" s="2">
         <v>50</v>
       </c>
-      <c r="G35" s="2"/>
       <c r="H35" s="1" t="s">
         <v>23</v>
       </c>
@@ -11295,7 +11291,6 @@
       <c r="F36" s="2">
         <v>50</v>
       </c>
-      <c r="G36" s="2"/>
       <c r="H36" s="1" t="s">
         <v>23</v>
       </c>
@@ -11319,7 +11314,6 @@
       <c r="F37" s="2">
         <v>50</v>
       </c>
-      <c r="G37" s="2"/>
       <c r="H37" s="1" t="s">
         <v>23</v>
       </c>
@@ -11343,7 +11337,6 @@
       <c r="F38" s="2">
         <v>50</v>
       </c>
-      <c r="G38" s="2"/>
       <c r="H38" s="1" t="s">
         <v>23</v>
       </c>
@@ -11367,7 +11360,6 @@
       <c r="F39" s="2">
         <v>50</v>
       </c>
-      <c r="G39" s="2"/>
       <c r="H39" s="1" t="s">
         <v>23</v>
       </c>
@@ -11391,7 +11383,6 @@
       <c r="F40" s="2">
         <v>50</v>
       </c>
-      <c r="G40" s="2"/>
       <c r="H40" s="1" t="s">
         <v>23</v>
       </c>
@@ -11415,7 +11406,6 @@
       <c r="F41" s="2">
         <v>50</v>
       </c>
-      <c r="G41" s="2"/>
       <c r="H41" s="1" t="s">
         <v>23</v>
       </c>
@@ -12255,7 +12245,6 @@
       <c r="F32" s="2">
         <v>50</v>
       </c>
-      <c r="G32" s="2"/>
       <c r="H32" s="1" t="s">
         <v>23</v>
       </c>
@@ -12279,7 +12268,6 @@
       <c r="F33" s="2">
         <v>50</v>
       </c>
-      <c r="G33" s="2"/>
       <c r="H33" s="1" t="s">
         <v>23</v>
       </c>
@@ -12303,7 +12291,6 @@
       <c r="F34" s="2">
         <v>50</v>
       </c>
-      <c r="G34" s="2"/>
       <c r="H34" s="1" t="s">
         <v>23</v>
       </c>
@@ -12327,7 +12314,6 @@
       <c r="F35" s="2">
         <v>50</v>
       </c>
-      <c r="G35" s="2"/>
       <c r="H35" s="1" t="s">
         <v>23</v>
       </c>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="36" activeTab="42"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -13435,7 +13435,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>-100</v>
+        <v>-120</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -14110,7 +14110,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="36" activeTab="42"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="82" activeTab="87"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -79,6 +79,23 @@
     <sheet name="get_fusion_parameters" sheetId="70" r:id="rId70"/>
     <sheet name="set_fusion_parameters" sheetId="71" r:id="rId71"/>
     <sheet name="solve_inv_kinematics" sheetId="72" r:id="rId72"/>
+    <sheet name="power_on" sheetId="73" r:id="rId73"/>
+    <sheet name="is_power_on" sheetId="74" r:id="rId74"/>
+    <sheet name="power_off" sheetId="75" r:id="rId75"/>
+    <sheet name="get_digital_inputs" sheetId="76" r:id="rId76"/>
+    <sheet name="get_collision_mode" sheetId="77" r:id="rId77"/>
+    <sheet name="set_collision_mode" sheetId="78" r:id="rId78"/>
+    <sheet name="set_collision_threshold" sheetId="79" r:id="rId79"/>
+    <sheet name="get_collision_threshold" sheetId="80" r:id="rId80"/>
+    <sheet name="set_torque_comp" sheetId="81" r:id="rId81"/>
+    <sheet name="get_torque_comp" sheetId="82" r:id="rId82"/>
+    <sheet name="write_move_c" sheetId="83" r:id="rId83"/>
+    <sheet name="set_color" sheetId="84" r:id="rId84"/>
+    <sheet name="set_tool_serial_baud_rate" sheetId="85" r:id="rId85"/>
+    <sheet name="set_tool_serial_timeout" sheetId="86" r:id="rId86"/>
+    <sheet name="get_tool_config" sheetId="87" r:id="rId87"/>
+    <sheet name="set_free_move_mode" sheetId="88" r:id="rId88"/>
+    <sheet name="get_free_move_mode" sheetId="89" r:id="rId89"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -98,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2787" uniqueCount="616">
   <si>
     <t>ID</t>
   </si>
@@ -1673,6 +1690,279 @@
   </si>
   <si>
     <t>获取速度融合规划参数超限</t>
+  </si>
+  <si>
+    <t>设置速度融合规划参数（恢复默认）</t>
+  </si>
+  <si>
+    <t>set_fusion_parameters</t>
+  </si>
+  <si>
+    <t>设置速度融合规划参数（融合关节速度）</t>
+  </si>
+  <si>
+    <t>设置速度融合规划参数（融合关节加速度）</t>
+  </si>
+  <si>
+    <t>设置速度融合规划参数（融合坐标速度）</t>
+  </si>
+  <si>
+    <t>设置速度融合规划参数（融合坐标加速度）</t>
+  </si>
+  <si>
+    <t>设置速度融合规划参数超限</t>
+  </si>
+  <si>
+    <t>target_coords</t>
+  </si>
+  <si>
+    <t>current_angles</t>
+  </si>
+  <si>
+    <t>正确计算运动学逆解</t>
+  </si>
+  <si>
+    <t>solve_inv_kinematics</t>
+  </si>
+  <si>
+    <t>[200.9, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
+  </si>
+  <si>
+    <t>[-0.37, 22.03, -118.21, 6.17, 0.0, -0.37]</t>
+  </si>
+  <si>
+    <t>设置目标坐标超限</t>
+  </si>
+  <si>
+    <t>[600, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
+  </si>
+  <si>
+    <t>正确计算运动学逆解无解</t>
+  </si>
+  <si>
+    <t>[400.9, -400.8, 298.4, 179.99, 0.0, -90.0]</t>
+  </si>
+  <si>
+    <t>No solution for conversion</t>
+  </si>
+  <si>
+    <t>logic</t>
+  </si>
+  <si>
+    <t>正常上电</t>
+  </si>
+  <si>
+    <t>power_on</t>
+  </si>
+  <si>
+    <t>急停状态上电</t>
+  </si>
+  <si>
+    <t>上电状态查询</t>
+  </si>
+  <si>
+    <t>is_power_on</t>
+  </si>
+  <si>
+    <t>下电状态查询</t>
+  </si>
+  <si>
+    <t>power_off</t>
+  </si>
+  <si>
+    <t>急停状态查询</t>
+  </si>
+  <si>
+    <t>emergency</t>
+  </si>
+  <si>
+    <t>正常下电</t>
+  </si>
+  <si>
+    <t>急停状态下电</t>
+  </si>
+  <si>
+    <t>获取末端所有引脚输入状态</t>
+  </si>
+  <si>
+    <t>get_digital_inputs</t>
+  </si>
+  <si>
+    <t>正确获取碰撞检测模式</t>
+  </si>
+  <si>
+    <t>get_collision_mode</t>
+  </si>
+  <si>
+    <t>正确设置碰撞检测模式</t>
+  </si>
+  <si>
+    <t>set_collision_mode</t>
+  </si>
+  <si>
+    <t>查看碰撞检测是否可触发</t>
+  </si>
+  <si>
+    <t>[81,82,83,84,85,86,87]</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>正确设置1关节碰撞阈值</t>
+  </si>
+  <si>
+    <t>set_collision_threshold</t>
+  </si>
+  <si>
+    <t>正确设置2关节碰撞阈值</t>
+  </si>
+  <si>
+    <t>正确设置3关节碰撞阈值</t>
+  </si>
+  <si>
+    <t>正确设置4关节碰撞阈值</t>
+  </si>
+  <si>
+    <t>正确设置5关节碰撞阈值</t>
+  </si>
+  <si>
+    <t>正确设置6关节碰撞阈值</t>
+  </si>
+  <si>
+    <t>设置碰撞阈值超限</t>
+  </si>
+  <si>
+    <t>正确获取碰撞阈值</t>
+  </si>
+  <si>
+    <t>get_collision_threshold</t>
+  </si>
+  <si>
+    <t>[100,100,100,100,100,100]</t>
+  </si>
+  <si>
+    <t>torque_comp</t>
+  </si>
+  <si>
+    <t>comp_value</t>
+  </si>
+  <si>
+    <t>正确设置1关节力矩参数</t>
+  </si>
+  <si>
+    <t>set_torque_comp</t>
+  </si>
+  <si>
+    <t>正确设置2关节力矩参数</t>
+  </si>
+  <si>
+    <t>正确设置3关节力矩参数</t>
+  </si>
+  <si>
+    <t>正确设置4关节力矩参数</t>
+  </si>
+  <si>
+    <t>正确设置5关节力矩参数</t>
+  </si>
+  <si>
+    <t>正确设置6关节力矩参数</t>
+  </si>
+  <si>
+    <t>设置力矩参数超限</t>
+  </si>
+  <si>
+    <t>设置阻抗开关超限</t>
+  </si>
+  <si>
+    <t>正确获取力矩补偿参数</t>
+  </si>
+  <si>
+    <t>get_torque_comp</t>
+  </si>
+  <si>
+    <t>[0,0,0,10,30,30,0,0,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>transpoint</t>
+  </si>
+  <si>
+    <t>endpoint</t>
+  </si>
+  <si>
+    <t>正确进行圆弧运动</t>
+  </si>
+  <si>
+    <t>write_move_c</t>
+  </si>
+  <si>
+    <t>[250.9, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>正确设置末端颜色（红）</t>
+  </si>
+  <si>
+    <t>set_color</t>
+  </si>
+  <si>
+    <t>正确设置末端颜色（绿）</t>
+  </si>
+  <si>
+    <t>正确设置末端颜色（蓝）</t>
+  </si>
+  <si>
+    <t>设置rgb值超限</t>
+  </si>
+  <si>
+    <t>正确设置末端485波特率</t>
+  </si>
+  <si>
+    <t>set_tool_serial_baud_rate</t>
+  </si>
+  <si>
+    <t>设置末端485波特率超限</t>
+  </si>
+  <si>
+    <t>正确设置末端485超时时间</t>
+  </si>
+  <si>
+    <t>set_tool_serial_timeout</t>
+  </si>
+  <si>
+    <t>设置末端485超时时间超限</t>
+  </si>
+  <si>
+    <t>正确获取末端485波特率，超时</t>
+  </si>
+  <si>
+    <t>get_tool_config</t>
+  </si>
+  <si>
+    <t>[115200,10000]</t>
+  </si>
+  <si>
+    <t>正确设置自由移动模式</t>
+  </si>
+  <si>
+    <t>set_free_move_mode</t>
+  </si>
+  <si>
+    <t>设置自由模式超限</t>
+  </si>
+  <si>
+    <t>正确获取自由移动模式</t>
+  </si>
+  <si>
+    <t>get_free_move_mode</t>
   </si>
 </sst>
 </file>
@@ -2746,7 +3036,7 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6296296296296" style="1" customWidth="1"/>
+    <col min="4" max="4" width="42.3333333333333" style="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="1"/>
     <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
@@ -2821,7 +3111,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="43.2" spans="1:8">
+    <row r="4" ht="28.8" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2847,7 +3137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="43.2" spans="1:8">
+    <row r="5" ht="28.8" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -8078,7 +8368,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -13015,7 +13305,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -19055,9 +19345,221 @@
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>200</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10000</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>500</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>10001</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="A15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -19066,9 +19568,808 @@
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7777777777778" style="1" customWidth="1"/>
+    <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.5555555555556" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="6" width="28.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>150</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>120</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="28.8" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>150</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2">
+        <v>120</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="28.8" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>251</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D10" s="2">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>100</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>100</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -19300,6 +20601,1119 @@
       </c>
       <c r="F11" s="1" t="s">
         <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.5555555555556" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="7" width="28.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>250</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>120</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>150</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2">
+        <v>120</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>251</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:8">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:8">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D10" s="2">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>100</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:8">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>100</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>100</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>150</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="34.6666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F2" s="2">
+        <v>50</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F3" s="2">
+        <v>101</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="7" width="20.4444444444444" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D2" s="2">
+        <v>255</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>255</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>255</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D5" s="2">
+        <v>256</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D2" s="2">
+        <v>115200</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D4" s="2">
+        <v>9600</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10001</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="5" width="34.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/mycobot_450.xlsx
+++ b/test_data/mycobot_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="82" activeTab="87"/>
+    <workbookView windowWidth="27948" windowHeight="12300" firstSheet="53" activeTab="53"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -17345,7 +17345,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -17365,7 +17365,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
